--- a/output/delivered/Data_requests_DR01_DR04_DR07_DR08_2026_10_09.xlsx
+++ b/output/delivered/Data_requests_DR01_DR04_DR07_DR08_2026_10_09.xlsx
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -296,6 +296,9 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -840,10 +843,10 @@
         <v>75</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -890,7 +893,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>The 17 items that could not be found, with the reason for each</t>
+          <t>The 16 items that could not be found, with the reason for each</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
@@ -5151,7 +5154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5170,7 +5173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>17 items across the four requests. Each was searched for in published sources; the reason is given.</t>
+          <t>16 items across the four requests. Each was searched for in published sources; the reason is given.</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5427,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>Vehicles by fuel within each class</t>
+          <t>Vehicles by year of age</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -5434,11 +5437,11 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>The bulletin splits fuel by province and the register splits class by province; nothing published crosses fuel with class.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15.5" customHeight="1">
+          <t>Lightstone holds the age profile and sells it; the register does not publish it. Only apparent retirements can be calculated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="29" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
           <t>DR07</t>
@@ -5446,7 +5449,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Vehicles by year of age</t>
+          <t>Electric trucks and electric light commercial vehicles sold</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -5456,11 +5459,11 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Lightstone holds the age profile and sells it; the register does not publish it. Only apparent retirements can be calculated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="29" customHeight="1">
+          <t>naamsa reports electric sales by drivetrain, not by segment (checked its fourth-quarter 2025 review). Benchmarks from other countries are on the HML response sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.5" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
           <t>DR07</t>
@@ -5468,7 +5471,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Electric trucks and electric light commercial vehicles sold</t>
+          <t>Fuel use of trucks, by year</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -5478,7 +5481,7 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>naamsa reports electric sales by drivetrain, not by segment (checked its fourth-quarter 2025 review). Benchmarks from other countries are on the HML response sheet.</t>
+          <t>Only the 2010 fleet figures above exist. No truck series by year was found.</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5493,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Fuel use of trucks, by year</t>
+          <t>Road freight in tonne-kilometres, by year</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -5500,29 +5503,29 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Only the 2010 fleet figures above exist. No truck series by year was found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.5" customHeight="1">
+          <t>The research group that models it (GAIN, Stellenbosch) shows yearly charts but publishes figures for single years only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="29" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>DR07</t>
+          <t>DR08</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>Road freight in tonne-kilometres, by year</t>
+          <t>Petrol and diesel output by plant</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Secunda and Astron Energy</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>The research group that models it (GAIN, Stellenbosch) shows yearly charts but publishes figures for single years only.</t>
+          <t>Sasol states Secunda's split (65% petrol, 35% diesel) but not the total it applies to. Glencore publishes no split for Astron. Sasol's annual filing and both companies' sites were checked on 9 October. Needs the operators.</t>
         </is>
       </c>
     </row>
@@ -5534,37 +5537,15 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Petrol and diesel output by plant</t>
+          <t>Petrol and diesel produced after 2021, on the department's basis</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>Secunda and Astron Energy</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>Sasol states Secunda's split (65% petrol, 35% diesel) but not the total it applies to. Glencore publishes no split for Astron. Sasol's annual filing and both companies' sites were checked on 9 October. Needs the operators.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="29" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>DR08</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Petrol and diesel produced after 2021, on the department's basis</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>The department has published no balance after 2021. The United Nations series runs to 2023 but does not match the department in the years they share.</t>
         </is>
@@ -16018,20 +15999,20 @@
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>58C</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Mpumalanga, Free State</t>
+          <t>Mpumalanga, KwaZulu Natal</t>
         </is>
       </c>
       <c r="C17" s="57" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>Amersfoort, Clocolan, Ermelo, Ficksburg, Frankfort, Heilbron</t>
+          <t>Piet Retief, Simdlangentsha, Wakkerstroom</t>
         </is>
       </c>
       <c r="E17" s="58" t="n">
@@ -16053,20 +16034,20 @@
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
         <is>
-          <t>58C</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Mpumalanga, KwaZulu Natal</t>
+          <t>Mpumalanga, Free State</t>
         </is>
       </c>
       <c r="C18" s="57" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D18" s="35" t="inlineStr">
         <is>
-          <t>Piet Retief, Simdlangentsha, Wakkerstroom</t>
+          <t>Amersfoort, Clocolan, Ermelo, Ficksburg, Frankfort, Heilbron</t>
         </is>
       </c>
       <c r="E18" s="58" t="n">
@@ -16578,7 +16559,7 @@
     <row r="33">
       <c r="A33" s="46" t="inlineStr">
         <is>
-          <t>64C</t>
+          <t>14C</t>
         </is>
       </c>
       <c r="B33" s="35" t="inlineStr">
@@ -16587,11 +16568,11 @@
         </is>
       </c>
       <c r="C33" s="57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="35" t="inlineStr">
         <is>
-          <t>Giyani, Malamulele</t>
+          <t>Dzanani North (East of Musina), Musina (Messina) (East of 30o longitude), Mutale</t>
         </is>
       </c>
       <c r="E33" s="58" t="n">
@@ -16613,7 +16594,7 @@
     <row r="34">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>14C</t>
+          <t>64C</t>
         </is>
       </c>
       <c r="B34" s="35" t="inlineStr">
@@ -16622,11 +16603,11 @@
         </is>
       </c>
       <c r="C34" s="57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" s="35" t="inlineStr">
         <is>
-          <t>Dzanani North (East of Musina), Musina (Messina) (East of 30o longitude), Mutale</t>
+          <t>Giyani, Malamulele</t>
         </is>
       </c>
       <c r="E34" s="58" t="n">
@@ -17843,7 +17824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T151"/>
+  <dimension ref="A1:T181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -17877,7 +17858,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>75 facts from sources (blue), 9 calculated (white), 6 not available (yellow). Petrol and diesel only. Figures reported for several years are set out one column a year; every row names its source.</t>
+          <t>75 facts from sources (blue), 21 calculated (white), 5 not available (yellow). Petrol and diesel only. Figures reported for several years are set out one column a year; every row names its source.</t>
         </is>
       </c>
     </row>
@@ -21866,493 +21847,581 @@
       <c r="R90" s="37" t="inlineStr"/>
       <c r="S90" s="37" t="inlineStr"/>
     </row>
-    <row r="91" ht="29" customHeight="1">
-      <c r="A91" s="41" t="inlineStr">
-        <is>
-          <t>Vehicles by fuel within each class</t>
-        </is>
-      </c>
-      <c r="B91" s="41" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C91" s="41" t="inlineStr">
+    <row r="91" ht="42.5" customHeight="1">
+      <c r="A91" s="37" t="inlineStr">
+        <is>
+          <t>Diesel vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B91" s="37" t="inlineStr">
+        <is>
+          <t>cars</t>
+        </is>
+      </c>
+      <c r="C91" s="37" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="D91" s="41" t="inlineStr"/>
-      <c r="E91" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="K91" s="41" t="n"/>
-      <c r="L91" s="41" t="n"/>
-      <c r="M91" s="41" t="n"/>
-      <c r="N91" s="41" t="n"/>
-      <c r="O91" s="41" t="n"/>
-      <c r="P91" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="Q91" s="41" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="R91" s="41" t="inlineStr"/>
-      <c r="S91" s="41" t="inlineStr">
-        <is>
-          <t>The bulletin splits fuel by province and the register splits class by province; nothing published crosses fuel with class.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="29" customHeight="1">
-      <c r="A92" s="35" t="inlineStr">
-        <is>
-          <t>Average age of vehicles</t>
-        </is>
-      </c>
-      <c r="B92" s="35" t="inlineStr">
-        <is>
-          <t>All vehicles and passenger vehicles</t>
-        </is>
-      </c>
-      <c r="C92" s="35" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D92" s="35" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E92" s="44" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="K92" s="35" t="n"/>
-      <c r="L92" s="35" t="n"/>
-      <c r="M92" s="35" t="n"/>
-      <c r="N92" s="35" t="n"/>
-      <c r="O92" s="35" t="n"/>
-      <c r="P92" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q92" s="35" t="inlineStr">
-        <is>
-          <t>Lightstone Auto Insights, April 2022</t>
-        </is>
-      </c>
-      <c r="R92" s="35" t="inlineStr"/>
-      <c r="S92" s="35" t="inlineStr">
-        <is>
-          <t>Ten years and six months, up from nine years and four months for passenger vehicles in 2014 and 2015.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="29" customHeight="1">
-      <c r="A93" s="41" t="inlineStr">
-        <is>
-          <t>Vehicles by year of age</t>
-        </is>
-      </c>
-      <c r="B93" s="41" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C93" s="41" t="inlineStr">
+      <c r="D91" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E91" s="62" t="n">
+        <v>1080644</v>
+      </c>
+      <c r="K91" s="37" t="n"/>
+      <c r="L91" s="37" t="n"/>
+      <c r="M91" s="37" t="n"/>
+      <c r="N91" s="37" t="n"/>
+      <c r="O91" s="37" t="n"/>
+      <c r="P91" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q91" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R91" s="37" t="inlineStr"/>
+      <c r="S91" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="42.5" customHeight="1">
+      <c r="A92" s="37" t="inlineStr">
+        <is>
+          <t>Diesel vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B92" s="37" t="inlineStr">
+        <is>
+          <t>light commercial</t>
+        </is>
+      </c>
+      <c r="C92" s="37" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="D93" s="41" t="inlineStr"/>
-      <c r="E93" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="K93" s="41" t="n"/>
-      <c r="L93" s="41" t="n"/>
-      <c r="M93" s="41" t="n"/>
-      <c r="N93" s="41" t="n"/>
-      <c r="O93" s="41" t="n"/>
-      <c r="P93" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="Q93" s="41" t="inlineStr">
-        <is>
-          <t>None published</t>
-        </is>
-      </c>
-      <c r="R93" s="41" t="inlineStr"/>
-      <c r="S93" s="41" t="inlineStr">
-        <is>
-          <t>Lightstone holds the age profile and sells it; the register does not publish it. Only apparent retirements can be calculated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="33" t="inlineStr">
-        <is>
-          <t>New vehicles and electric share</t>
-        </is>
-      </c>
-      <c r="B95" s="33" t="n"/>
-      <c r="C95" s="33" t="n"/>
-      <c r="D95" s="33" t="n"/>
-      <c r="E95" s="33" t="n"/>
-      <c r="F95" s="33" t="n"/>
-      <c r="G95" s="33" t="n"/>
-      <c r="H95" s="33" t="n"/>
-      <c r="I95" s="33" t="n"/>
-      <c r="J95" s="33" t="n"/>
-      <c r="K95" s="33" t="n"/>
-      <c r="L95" s="33" t="n"/>
-      <c r="M95" s="33" t="n"/>
-      <c r="N95" s="33" t="n"/>
-      <c r="O95" s="33" t="n"/>
-      <c r="P95" s="33" t="n"/>
-      <c r="Q95" s="33" t="n"/>
-      <c r="R95" s="33" t="n"/>
-      <c r="S95" s="33" t="n"/>
-      <c r="T95" s="33" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="34" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B96" s="34" t="inlineStr">
-        <is>
-          <t>Covers</t>
-        </is>
-      </c>
-      <c r="C96" s="34" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D96" s="34" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="E96" s="34" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="K96" s="34" t="n"/>
-      <c r="L96" s="34" t="n"/>
-      <c r="M96" s="34" t="n"/>
-      <c r="N96" s="34" t="n"/>
-      <c r="O96" s="34" t="n"/>
-      <c r="P96" s="34" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="Q96" s="34" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="R96" s="34" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="S96" s="34" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="15.5" customHeight="1">
-      <c r="A97" s="35" t="inlineStr">
-        <is>
-          <t>New vehicles sold, by segment</t>
-        </is>
-      </c>
-      <c r="B97" s="35" t="inlineStr">
+      <c r="D92" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E92" s="62" t="n">
+        <v>1506107</v>
+      </c>
+      <c r="K92" s="37" t="n"/>
+      <c r="L92" s="37" t="n"/>
+      <c r="M92" s="37" t="n"/>
+      <c r="N92" s="37" t="n"/>
+      <c r="O92" s="37" t="n"/>
+      <c r="P92" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q92" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R92" s="37" t="inlineStr"/>
+      <c r="S92" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="42.5" customHeight="1">
+      <c r="A93" s="37" t="inlineStr">
+        <is>
+          <t>Diesel vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B93" s="37" t="inlineStr">
+        <is>
+          <t>trucks</t>
+        </is>
+      </c>
+      <c r="C93" s="37" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D93" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E93" s="62" t="n">
+        <v>388778</v>
+      </c>
+      <c r="K93" s="37" t="n"/>
+      <c r="L93" s="37" t="n"/>
+      <c r="M93" s="37" t="n"/>
+      <c r="N93" s="37" t="n"/>
+      <c r="O93" s="37" t="n"/>
+      <c r="P93" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q93" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R93" s="37" t="inlineStr"/>
+      <c r="S93" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="42.5" customHeight="1">
+      <c r="A94" s="37" t="inlineStr">
+        <is>
+          <t>Diesel vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B94" s="37" t="inlineStr">
+        <is>
+          <t>buses</t>
+        </is>
+      </c>
+      <c r="C94" s="37" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D94" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E94" s="62" t="n">
+        <v>64982</v>
+      </c>
+      <c r="K94" s="37" t="n"/>
+      <c r="L94" s="37" t="n"/>
+      <c r="M94" s="37" t="n"/>
+      <c r="N94" s="37" t="n"/>
+      <c r="O94" s="37" t="n"/>
+      <c r="P94" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q94" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R94" s="37" t="inlineStr"/>
+      <c r="S94" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="42.5" customHeight="1">
+      <c r="A95" s="37" t="inlineStr">
+        <is>
+          <t>Diesel vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B95" s="37" t="inlineStr">
+        <is>
+          <t>minibuses</t>
+        </is>
+      </c>
+      <c r="C95" s="37" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D95" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E95" s="62" t="n">
+        <v>54087</v>
+      </c>
+      <c r="K95" s="37" t="n"/>
+      <c r="L95" s="37" t="n"/>
+      <c r="M95" s="37" t="n"/>
+      <c r="N95" s="37" t="n"/>
+      <c r="O95" s="37" t="n"/>
+      <c r="P95" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q95" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R95" s="37" t="inlineStr"/>
+      <c r="S95" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="42.5" customHeight="1">
+      <c r="A96" s="37" t="inlineStr">
+        <is>
+          <t>Diesel vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B96" s="37" t="inlineStr">
+        <is>
+          <t>motorcycles</t>
+        </is>
+      </c>
+      <c r="C96" s="37" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D96" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E96" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="37" t="n"/>
+      <c r="L96" s="37" t="n"/>
+      <c r="M96" s="37" t="n"/>
+      <c r="N96" s="37" t="n"/>
+      <c r="O96" s="37" t="n"/>
+      <c r="P96" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q96" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R96" s="37" t="inlineStr"/>
+      <c r="S96" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="42.5" customHeight="1">
+      <c r="A97" s="37" t="inlineStr">
+        <is>
+          <t>Diesel vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B97" s="37" t="inlineStr">
+        <is>
+          <t>other self propelled</t>
+        </is>
+      </c>
+      <c r="C97" s="37" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D97" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E97" s="62" t="n">
+        <v>238955</v>
+      </c>
+      <c r="K97" s="37" t="n"/>
+      <c r="L97" s="37" t="n"/>
+      <c r="M97" s="37" t="n"/>
+      <c r="N97" s="37" t="n"/>
+      <c r="O97" s="37" t="n"/>
+      <c r="P97" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q97" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R97" s="37" t="inlineStr"/>
+      <c r="S97" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="42.5" customHeight="1">
+      <c r="A98" s="37" t="inlineStr">
+        <is>
+          <t>Petrol vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B98" s="37" t="inlineStr">
         <is>
           <t>cars</t>
         </is>
       </c>
-      <c r="C97" s="35" t="inlineStr">
+      <c r="C98" s="37" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="D97" s="35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E97" s="36" t="n">
-        <v>422463</v>
-      </c>
-      <c r="K97" s="35" t="n"/>
-      <c r="L97" s="35" t="n"/>
-      <c r="M97" s="35" t="n"/>
-      <c r="N97" s="35" t="n"/>
-      <c r="O97" s="35" t="n"/>
-      <c r="P97" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q97" s="35" t="inlineStr">
-        <is>
-          <t>naamsa, industry vehicle sales</t>
-        </is>
-      </c>
-      <c r="R97" s="35" t="inlineStr"/>
-      <c r="S97" s="35" t="inlineStr"/>
-    </row>
-    <row r="98" ht="15.5" customHeight="1">
-      <c r="A98" s="35" t="inlineStr">
-        <is>
-          <t>New vehicles sold, by segment</t>
-        </is>
-      </c>
-      <c r="B98" s="35" t="inlineStr">
+      <c r="D98" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E98" s="62" t="n">
+        <v>6713520</v>
+      </c>
+      <c r="K98" s="37" t="n"/>
+      <c r="L98" s="37" t="n"/>
+      <c r="M98" s="37" t="n"/>
+      <c r="N98" s="37" t="n"/>
+      <c r="O98" s="37" t="n"/>
+      <c r="P98" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q98" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R98" s="37" t="inlineStr"/>
+      <c r="S98" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="42.5" customHeight="1">
+      <c r="A99" s="37" t="inlineStr">
+        <is>
+          <t>Petrol vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B99" s="37" t="inlineStr">
         <is>
           <t>light commercial</t>
         </is>
       </c>
-      <c r="C98" s="35" t="inlineStr">
+      <c r="C99" s="37" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="D98" s="35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E98" s="36" t="n">
-        <v>143964</v>
-      </c>
-      <c r="K98" s="35" t="n"/>
-      <c r="L98" s="35" t="n"/>
-      <c r="M98" s="35" t="n"/>
-      <c r="N98" s="35" t="n"/>
-      <c r="O98" s="35" t="n"/>
-      <c r="P98" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q98" s="35" t="inlineStr">
-        <is>
-          <t>naamsa, industry vehicle sales</t>
-        </is>
-      </c>
-      <c r="R98" s="35" t="inlineStr"/>
-      <c r="S98" s="35" t="inlineStr"/>
-    </row>
-    <row r="99" ht="15.5" customHeight="1">
-      <c r="A99" s="35" t="inlineStr">
-        <is>
-          <t>New vehicles sold, by segment</t>
-        </is>
-      </c>
-      <c r="B99" s="35" t="inlineStr">
-        <is>
-          <t>medium and heavy commercial</t>
-        </is>
-      </c>
-      <c r="C99" s="35" t="inlineStr">
+      <c r="D99" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E99" s="62" t="n">
+        <v>1183203</v>
+      </c>
+      <c r="K99" s="37" t="n"/>
+      <c r="L99" s="37" t="n"/>
+      <c r="M99" s="37" t="n"/>
+      <c r="N99" s="37" t="n"/>
+      <c r="O99" s="37" t="n"/>
+      <c r="P99" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q99" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R99" s="37" t="inlineStr"/>
+      <c r="S99" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="42.5" customHeight="1">
+      <c r="A100" s="37" t="inlineStr">
+        <is>
+          <t>Petrol vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B100" s="37" t="inlineStr">
+        <is>
+          <t>trucks</t>
+        </is>
+      </c>
+      <c r="C100" s="37" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="D99" s="35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E99" s="36" t="n">
-        <v>30911</v>
-      </c>
-      <c r="K99" s="35" t="n"/>
-      <c r="L99" s="35" t="n"/>
-      <c r="M99" s="35" t="n"/>
-      <c r="N99" s="35" t="n"/>
-      <c r="O99" s="35" t="n"/>
-      <c r="P99" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q99" s="35" t="inlineStr">
-        <is>
-          <t>naamsa, industry vehicle sales</t>
-        </is>
-      </c>
-      <c r="R99" s="35" t="inlineStr"/>
-      <c r="S99" s="35" t="inlineStr"/>
-    </row>
-    <row r="100" ht="15.5" customHeight="1">
-      <c r="A100" s="35" t="inlineStr">
-        <is>
-          <t>Electric and hybrid vehicles sold</t>
-        </is>
-      </c>
-      <c r="B100" s="35" t="inlineStr">
-        <is>
-          <t>battery electric</t>
-        </is>
-      </c>
-      <c r="C100" s="35" t="inlineStr">
+      <c r="D100" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E100" s="62" t="n">
+        <v>3571</v>
+      </c>
+      <c r="K100" s="37" t="n"/>
+      <c r="L100" s="37" t="n"/>
+      <c r="M100" s="37" t="n"/>
+      <c r="N100" s="37" t="n"/>
+      <c r="O100" s="37" t="n"/>
+      <c r="P100" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q100" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R100" s="37" t="inlineStr"/>
+      <c r="S100" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="42.5" customHeight="1">
+      <c r="A101" s="37" t="inlineStr">
+        <is>
+          <t>Petrol vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B101" s="37" t="inlineStr">
+        <is>
+          <t>buses</t>
+        </is>
+      </c>
+      <c r="C101" s="37" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="D100" s="35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E100" s="36" t="n">
-        <v>1088</v>
-      </c>
-      <c r="K100" s="35" t="n"/>
-      <c r="L100" s="35" t="n"/>
-      <c r="M100" s="35" t="n"/>
-      <c r="N100" s="35" t="n"/>
-      <c r="O100" s="35" t="n"/>
-      <c r="P100" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q100" s="35" t="inlineStr">
-        <is>
-          <t>naamsa, new energy vehicle sales</t>
-        </is>
-      </c>
-      <c r="R100" s="35" t="inlineStr"/>
-      <c r="S100" s="35" t="inlineStr"/>
-    </row>
-    <row r="101" ht="15.5" customHeight="1">
-      <c r="A101" s="35" t="inlineStr">
-        <is>
-          <t>Electric and hybrid vehicles sold</t>
-        </is>
-      </c>
-      <c r="B101" s="35" t="inlineStr">
-        <is>
-          <t>plug-in hybrid</t>
-        </is>
-      </c>
-      <c r="C101" s="35" t="inlineStr">
+      <c r="D101" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E101" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="37" t="n"/>
+      <c r="L101" s="37" t="n"/>
+      <c r="M101" s="37" t="n"/>
+      <c r="N101" s="37" t="n"/>
+      <c r="O101" s="37" t="n"/>
+      <c r="P101" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q101" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R101" s="37" t="inlineStr"/>
+      <c r="S101" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="42.5" customHeight="1">
+      <c r="A102" s="37" t="inlineStr">
+        <is>
+          <t>Petrol vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B102" s="37" t="inlineStr">
+        <is>
+          <t>minibuses</t>
+        </is>
+      </c>
+      <c r="C102" s="37" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="D101" s="35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E101" s="36" t="n">
-        <v>2810</v>
-      </c>
-      <c r="K101" s="35" t="n"/>
-      <c r="L101" s="35" t="n"/>
-      <c r="M101" s="35" t="n"/>
-      <c r="N101" s="35" t="n"/>
-      <c r="O101" s="35" t="n"/>
-      <c r="P101" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q101" s="35" t="inlineStr">
-        <is>
-          <t>naamsa, new energy vehicle sales</t>
-        </is>
-      </c>
-      <c r="R101" s="35" t="inlineStr"/>
-      <c r="S101" s="35" t="inlineStr"/>
-    </row>
-    <row r="102" ht="15.5" customHeight="1">
-      <c r="A102" s="35" t="inlineStr">
-        <is>
-          <t>Electric and hybrid vehicles sold</t>
-        </is>
-      </c>
-      <c r="B102" s="35" t="inlineStr">
-        <is>
-          <t>conventional hybrid</t>
-        </is>
-      </c>
-      <c r="C102" s="35" t="inlineStr">
+      <c r="D102" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E102" s="62" t="n">
+        <v>301148</v>
+      </c>
+      <c r="K102" s="37" t="n"/>
+      <c r="L102" s="37" t="n"/>
+      <c r="M102" s="37" t="n"/>
+      <c r="N102" s="37" t="n"/>
+      <c r="O102" s="37" t="n"/>
+      <c r="P102" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q102" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R102" s="37" t="inlineStr"/>
+      <c r="S102" s="37" t="inlineStr">
+        <is>
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="42.5" customHeight="1">
+      <c r="A103" s="37" t="inlineStr">
+        <is>
+          <t>Petrol vehicles by class, estimated</t>
+        </is>
+      </c>
+      <c r="B103" s="37" t="inlineStr">
+        <is>
+          <t>motorcycles</t>
+        </is>
+      </c>
+      <c r="C103" s="37" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="D102" s="35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E102" s="36" t="n">
-        <v>12818</v>
-      </c>
-      <c r="K102" s="35" t="n"/>
-      <c r="L102" s="35" t="n"/>
-      <c r="M102" s="35" t="n"/>
-      <c r="N102" s="35" t="n"/>
-      <c r="O102" s="35" t="n"/>
-      <c r="P102" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q102" s="35" t="inlineStr">
-        <is>
-          <t>naamsa, new energy vehicle sales</t>
-        </is>
-      </c>
-      <c r="R102" s="35" t="inlineStr"/>
-      <c r="S102" s="35" t="inlineStr"/>
-    </row>
-    <row r="103" ht="15.5" customHeight="1">
-      <c r="A103" s="37" t="inlineStr">
-        <is>
-          <t>Share of new vehicles sold</t>
-        </is>
-      </c>
-      <c r="B103" s="37" t="inlineStr">
-        <is>
-          <t>battery electric</t>
-        </is>
-      </c>
-      <c r="C103" s="37" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
       <c r="D103" s="37" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E103" s="38" t="n">
-        <v>0.18</v>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E103" s="62" t="n">
+        <v>349215</v>
       </c>
       <c r="K103" s="37" t="n"/>
       <c r="L103" s="37" t="n"/>
@@ -22366,39 +22435,39 @@
       </c>
       <c r="Q103" s="37" t="inlineStr">
         <is>
-          <t>Calculated from the two naamsa series</t>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
         </is>
       </c>
       <c r="R103" s="37" t="inlineStr"/>
       <c r="S103" s="37" t="inlineStr">
         <is>
-          <t>Battery electric sales fell from 2024 to 2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="15.5" customHeight="1">
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="42.5" customHeight="1">
       <c r="A104" s="37" t="inlineStr">
         <is>
-          <t>Share of new vehicles sold</t>
+          <t>Petrol vehicles by class, estimated</t>
         </is>
       </c>
       <c r="B104" s="37" t="inlineStr">
         <is>
-          <t>plug-in hybrid</t>
+          <t>other self propelled</t>
         </is>
       </c>
       <c r="C104" s="37" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>vehicles</t>
         </is>
       </c>
       <c r="D104" s="37" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E104" s="38" t="n">
-        <v>0.47</v>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E104" s="62" t="n">
+        <v>0</v>
       </c>
       <c r="K104" s="37" t="n"/>
       <c r="L104" s="37" t="n"/>
@@ -22412,25 +22481,25 @@
       </c>
       <c r="Q104" s="37" t="inlineStr">
         <is>
-          <t>Calculated from the two naamsa series</t>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
         </is>
       </c>
       <c r="R104" s="37" t="inlineStr"/>
       <c r="S104" s="37" t="inlineStr">
         <is>
-          <t>Battery electric sales fell from 2024 to 2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="15.5" customHeight="1">
+          <t>Estimated, not published: each class's diesel share in the 2010 fleet (Stone et al. 2018) moved by one common factor so the classes add up to the bulletin's diesel total. Nothing published crosses fuel with class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="42.5" customHeight="1">
       <c r="A105" s="37" t="inlineStr">
         <is>
-          <t>Share of new vehicles sold</t>
+          <t>Diesel share by class, estimated</t>
         </is>
       </c>
       <c r="B105" s="37" t="inlineStr">
         <is>
-          <t>conventional hybrid</t>
+          <t>cars</t>
         </is>
       </c>
       <c r="C105" s="37" t="inlineStr">
@@ -22440,11 +22509,11 @@
       </c>
       <c r="D105" s="37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>December 2023</t>
         </is>
       </c>
       <c r="E105" s="38" t="n">
-        <v>2.15</v>
+        <v>13.9</v>
       </c>
       <c r="K105" s="37" t="n"/>
       <c r="L105" s="37" t="n"/>
@@ -22458,995 +22527,1177 @@
       </c>
       <c r="Q105" s="37" t="inlineStr">
         <is>
-          <t>Calculated from the two naamsa series</t>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
         </is>
       </c>
       <c r="R105" s="37" t="inlineStr"/>
       <c r="S105" s="37" t="inlineStr">
         <is>
-          <t>Battery electric sales fell from 2024 to 2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="29" customHeight="1">
-      <c r="A106" s="35" t="inlineStr">
-        <is>
-          <t>Diesel share of new light vehicles sold</t>
-        </is>
-      </c>
-      <c r="B106" s="35" t="inlineStr">
-        <is>
-          <t>New light-duty vehicles</t>
-        </is>
-      </c>
-      <c r="C106" s="35" t="inlineStr">
+          <t>The common factor is 2.08: diesel has gained share in every mixed class since 2010. Tractors and plant are taken as all diesel, an assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="42.5" customHeight="1">
+      <c r="A106" s="37" t="inlineStr">
+        <is>
+          <t>Diesel share by class, estimated</t>
+        </is>
+      </c>
+      <c r="B106" s="37" t="inlineStr">
+        <is>
+          <t>light commercial</t>
+        </is>
+      </c>
+      <c r="C106" s="37" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D106" s="35" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="E106" s="36" t="n">
+      <c r="D106" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E106" s="38" t="n">
+        <v>56</v>
+      </c>
+      <c r="K106" s="37" t="n"/>
+      <c r="L106" s="37" t="n"/>
+      <c r="M106" s="37" t="n"/>
+      <c r="N106" s="37" t="n"/>
+      <c r="O106" s="37" t="n"/>
+      <c r="P106" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q106" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R106" s="37" t="inlineStr"/>
+      <c r="S106" s="37" t="inlineStr">
+        <is>
+          <t>The common factor is 2.08: diesel has gained share in every mixed class since 2010. Tractors and plant are taken as all diesel, an assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="42.5" customHeight="1">
+      <c r="A107" s="37" t="inlineStr">
+        <is>
+          <t>Diesel share by class, estimated</t>
+        </is>
+      </c>
+      <c r="B107" s="37" t="inlineStr">
+        <is>
+          <t>trucks</t>
+        </is>
+      </c>
+      <c r="C107" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D107" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E107" s="38" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="K107" s="37" t="n"/>
+      <c r="L107" s="37" t="n"/>
+      <c r="M107" s="37" t="n"/>
+      <c r="N107" s="37" t="n"/>
+      <c r="O107" s="37" t="n"/>
+      <c r="P107" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q107" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R107" s="37" t="inlineStr"/>
+      <c r="S107" s="37" t="inlineStr">
+        <is>
+          <t>The common factor is 2.08: diesel has gained share in every mixed class since 2010. Tractors and plant are taken as all diesel, an assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="42.5" customHeight="1">
+      <c r="A108" s="37" t="inlineStr">
+        <is>
+          <t>Diesel share by class, estimated</t>
+        </is>
+      </c>
+      <c r="B108" s="37" t="inlineStr">
+        <is>
+          <t>buses</t>
+        </is>
+      </c>
+      <c r="C108" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D108" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E108" s="63" t="n">
+        <v>100</v>
+      </c>
+      <c r="K108" s="37" t="n"/>
+      <c r="L108" s="37" t="n"/>
+      <c r="M108" s="37" t="n"/>
+      <c r="N108" s="37" t="n"/>
+      <c r="O108" s="37" t="n"/>
+      <c r="P108" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q108" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R108" s="37" t="inlineStr"/>
+      <c r="S108" s="37" t="inlineStr">
+        <is>
+          <t>The common factor is 2.08: diesel has gained share in every mixed class since 2010. Tractors and plant are taken as all diesel, an assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="42.5" customHeight="1">
+      <c r="A109" s="37" t="inlineStr">
+        <is>
+          <t>Diesel share by class, estimated</t>
+        </is>
+      </c>
+      <c r="B109" s="37" t="inlineStr">
+        <is>
+          <t>minibuses</t>
+        </is>
+      </c>
+      <c r="C109" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D109" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E109" s="38" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="K109" s="37" t="n"/>
+      <c r="L109" s="37" t="n"/>
+      <c r="M109" s="37" t="n"/>
+      <c r="N109" s="37" t="n"/>
+      <c r="O109" s="37" t="n"/>
+      <c r="P109" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q109" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R109" s="37" t="inlineStr"/>
+      <c r="S109" s="37" t="inlineStr">
+        <is>
+          <t>The common factor is 2.08: diesel has gained share in every mixed class since 2010. Tractors and plant are taken as all diesel, an assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="42.5" customHeight="1">
+      <c r="A110" s="37" t="inlineStr">
+        <is>
+          <t>Diesel share by class, estimated</t>
+        </is>
+      </c>
+      <c r="B110" s="37" t="inlineStr">
+        <is>
+          <t>motorcycles</t>
+        </is>
+      </c>
+      <c r="C110" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D110" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E110" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="37" t="n"/>
+      <c r="L110" s="37" t="n"/>
+      <c r="M110" s="37" t="n"/>
+      <c r="N110" s="37" t="n"/>
+      <c r="O110" s="37" t="n"/>
+      <c r="P110" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q110" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R110" s="37" t="inlineStr"/>
+      <c r="S110" s="37" t="inlineStr">
+        <is>
+          <t>The common factor is 2.08: diesel has gained share in every mixed class since 2010. Tractors and plant are taken as all diesel, an assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="42.5" customHeight="1">
+      <c r="A111" s="37" t="inlineStr">
+        <is>
+          <t>Diesel share by class, estimated</t>
+        </is>
+      </c>
+      <c r="B111" s="37" t="inlineStr">
+        <is>
+          <t>other self propelled</t>
+        </is>
+      </c>
+      <c r="C111" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D111" s="37" t="inlineStr">
+        <is>
+          <t>December 2023</t>
+        </is>
+      </c>
+      <c r="E111" s="63" t="n">
+        <v>100</v>
+      </c>
+      <c r="K111" s="37" t="n"/>
+      <c r="L111" s="37" t="n"/>
+      <c r="M111" s="37" t="n"/>
+      <c r="N111" s="37" t="n"/>
+      <c r="O111" s="37" t="n"/>
+      <c r="P111" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q111" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the register (December 2023), the transport bulletin (December 2023) and Stone et al. (2018)</t>
+        </is>
+      </c>
+      <c r="R111" s="37" t="inlineStr"/>
+      <c r="S111" s="37" t="inlineStr">
+        <is>
+          <t>The common factor is 2.08: diesel has gained share in every mixed class since 2010. Tractors and plant are taken as all diesel, an assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="29" customHeight="1">
+      <c r="A112" s="35" t="inlineStr">
+        <is>
+          <t>Average age of vehicles</t>
+        </is>
+      </c>
+      <c r="B112" s="35" t="inlineStr">
+        <is>
+          <t>All vehicles and passenger vehicles</t>
+        </is>
+      </c>
+      <c r="C112" s="35" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D112" s="35" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E112" s="44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K112" s="35" t="n"/>
+      <c r="L112" s="35" t="n"/>
+      <c r="M112" s="35" t="n"/>
+      <c r="N112" s="35" t="n"/>
+      <c r="O112" s="35" t="n"/>
+      <c r="P112" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q112" s="35" t="inlineStr">
+        <is>
+          <t>Lightstone Auto Insights, April 2022</t>
+        </is>
+      </c>
+      <c r="R112" s="35" t="inlineStr"/>
+      <c r="S112" s="35" t="inlineStr">
+        <is>
+          <t>Ten years and six months, up from nine years and four months for passenger vehicles in 2014 and 2015.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="29" customHeight="1">
+      <c r="A113" s="41" t="inlineStr">
+        <is>
+          <t>Vehicles by year of age</t>
+        </is>
+      </c>
+      <c r="B113" s="41" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C113" s="41" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D113" s="41" t="inlineStr"/>
+      <c r="E113" s="41" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="K113" s="41" t="n"/>
+      <c r="L113" s="41" t="n"/>
+      <c r="M113" s="41" t="n"/>
+      <c r="N113" s="41" t="n"/>
+      <c r="O113" s="41" t="n"/>
+      <c r="P113" s="41" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q113" s="41" t="inlineStr">
+        <is>
+          <t>None published</t>
+        </is>
+      </c>
+      <c r="R113" s="41" t="inlineStr"/>
+      <c r="S113" s="41" t="inlineStr">
+        <is>
+          <t>Lightstone holds the age profile and sells it; the register does not publish it. Only apparent retirements can be calculated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="33" t="inlineStr">
+        <is>
+          <t>New vehicles and electric share</t>
+        </is>
+      </c>
+      <c r="B115" s="33" t="n"/>
+      <c r="C115" s="33" t="n"/>
+      <c r="D115" s="33" t="n"/>
+      <c r="E115" s="33" t="n"/>
+      <c r="F115" s="33" t="n"/>
+      <c r="G115" s="33" t="n"/>
+      <c r="H115" s="33" t="n"/>
+      <c r="I115" s="33" t="n"/>
+      <c r="J115" s="33" t="n"/>
+      <c r="K115" s="33" t="n"/>
+      <c r="L115" s="33" t="n"/>
+      <c r="M115" s="33" t="n"/>
+      <c r="N115" s="33" t="n"/>
+      <c r="O115" s="33" t="n"/>
+      <c r="P115" s="33" t="n"/>
+      <c r="Q115" s="33" t="n"/>
+      <c r="R115" s="33" t="n"/>
+      <c r="S115" s="33" t="n"/>
+      <c r="T115" s="33" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="34" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B116" s="34" t="inlineStr">
+        <is>
+          <t>Covers</t>
+        </is>
+      </c>
+      <c r="C116" s="34" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D116" s="34" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E116" s="42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F116" s="42" t="n">
+        <v>2027</v>
+      </c>
+      <c r="G116" s="42" t="n">
+        <v>2028</v>
+      </c>
+      <c r="H116" s="42" t="n">
+        <v>2029</v>
+      </c>
+      <c r="I116" s="42" t="n">
+        <v>2030</v>
+      </c>
+      <c r="J116" s="42" t="n">
+        <v>2031</v>
+      </c>
+      <c r="K116" s="42" t="n">
+        <v>2032</v>
+      </c>
+      <c r="L116" s="42" t="n">
+        <v>2033</v>
+      </c>
+      <c r="M116" s="42" t="n">
+        <v>2034</v>
+      </c>
+      <c r="N116" s="42" t="n">
+        <v>2035</v>
+      </c>
+      <c r="O116" s="34" t="n"/>
+      <c r="P116" s="34" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Q116" s="34" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="R116" s="34" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="S116" s="34" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="42.5" customHeight="1">
+      <c r="A117" s="37" t="inlineStr">
+        <is>
+          <t>Electric share of new light commercial sales, forecast</t>
+        </is>
+      </c>
+      <c r="B117" s="37" t="inlineStr">
+        <is>
+          <t>Low case</t>
+        </is>
+      </c>
+      <c r="C117" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D117" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="37" t="n"/>
+      <c r="P117" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q117" s="37" t="inlineStr">
+        <is>
+          <t>Analyst forecast from the lever cases</t>
+        </is>
+      </c>
+      <c r="R117" s="37" t="inlineStr"/>
+      <c r="S117" s="37" t="inlineStr">
+        <is>
+          <t>A forecast of ours, not a published one. The 2030 and 2035 shares are the three cases on the HML response sheet, set against benchmarks abroad; the path between them is a straight line from nil in 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="42.5" customHeight="1">
+      <c r="A118" s="37" t="inlineStr">
+        <is>
+          <t>Electric share of new light commercial sales, forecast</t>
+        </is>
+      </c>
+      <c r="B118" s="37" t="inlineStr">
+        <is>
+          <t>Medium case</t>
+        </is>
+      </c>
+      <c r="C118" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D118" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E118" s="40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F118" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G118" s="40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H118" s="40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I118" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K118" s="40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L118" s="40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M118" s="40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N118" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="O118" s="37" t="n"/>
+      <c r="P118" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q118" s="37" t="inlineStr">
+        <is>
+          <t>Analyst forecast from the lever cases</t>
+        </is>
+      </c>
+      <c r="R118" s="37" t="inlineStr"/>
+      <c r="S118" s="37" t="inlineStr">
+        <is>
+          <t>A forecast of ours, not a published one. The 2030 and 2035 shares are the three cases on the HML response sheet, set against benchmarks abroad; the path between them is a straight line from nil in 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="42.5" customHeight="1">
+      <c r="A119" s="37" t="inlineStr">
+        <is>
+          <t>Electric share of new light commercial sales, forecast</t>
+        </is>
+      </c>
+      <c r="B119" s="37" t="inlineStr">
+        <is>
+          <t>High case</t>
+        </is>
+      </c>
+      <c r="C119" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D119" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E119" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I119" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J119" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="K119" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="L119" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="M119" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="N119" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="O119" s="37" t="n"/>
+      <c r="P119" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q119" s="37" t="inlineStr">
+        <is>
+          <t>Analyst forecast from the lever cases</t>
+        </is>
+      </c>
+      <c r="R119" s="37" t="inlineStr"/>
+      <c r="S119" s="37" t="inlineStr">
+        <is>
+          <t>A forecast of ours, not a published one. The 2030 and 2035 shares are the three cases on the HML response sheet, set against benchmarks abroad; the path between them is a straight line from nil in 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="29" customHeight="1">
+      <c r="A120" s="37" t="inlineStr">
+        <is>
+          <t>Electric light commercial vehicles on the road, forecast</t>
+        </is>
+      </c>
+      <c r="B120" s="37" t="inlineStr">
+        <is>
+          <t>Low case</t>
+        </is>
+      </c>
+      <c r="C120" s="37" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D120" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="37" t="n"/>
+      <c r="P120" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q120" s="37" t="inlineStr">
+        <is>
+          <t>Forecast share x naamsa's sales outlook, added up</t>
+        </is>
+      </c>
+      <c r="R120" s="37" t="inlineStr"/>
+      <c r="S120" s="37" t="inlineStr">
+        <is>
+          <t>0.0% of today's light commercial fleet by 2035. Sales after 2027 are held at naamsa's 2027 projection; no electric vehicle is scrapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="29" customHeight="1">
+      <c r="A121" s="37" t="inlineStr">
+        <is>
+          <t>Electric light commercial vehicles on the road, forecast</t>
+        </is>
+      </c>
+      <c r="B121" s="37" t="inlineStr">
+        <is>
+          <t>Medium case</t>
+        </is>
+      </c>
+      <c r="C121" s="37" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D121" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E121" s="43" t="n">
+        <v>320</v>
+      </c>
+      <c r="F121" s="43" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G121" s="43" t="n">
+        <v>2120</v>
+      </c>
+      <c r="H121" s="43" t="n">
+        <v>3560</v>
+      </c>
+      <c r="I121" s="43" t="n">
+        <v>5360</v>
+      </c>
+      <c r="J121" s="43" t="n">
+        <v>8600</v>
+      </c>
+      <c r="K121" s="43" t="n">
+        <v>13280</v>
+      </c>
+      <c r="L121" s="43" t="n">
+        <v>19400</v>
+      </c>
+      <c r="M121" s="43" t="n">
+        <v>26960</v>
+      </c>
+      <c r="N121" s="43" t="n">
+        <v>35960</v>
+      </c>
+      <c r="O121" s="37" t="n"/>
+      <c r="P121" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q121" s="37" t="inlineStr">
+        <is>
+          <t>Forecast share x naamsa's sales outlook, added up</t>
+        </is>
+      </c>
+      <c r="R121" s="37" t="inlineStr"/>
+      <c r="S121" s="37" t="inlineStr">
+        <is>
+          <t>1.3% of today's light commercial fleet by 2035. Sales after 2027 are held at naamsa's 2027 projection; no electric vehicle is scrapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="29" customHeight="1">
+      <c r="A122" s="37" t="inlineStr">
+        <is>
+          <t>Electric light commercial vehicles on the road, forecast</t>
+        </is>
+      </c>
+      <c r="B122" s="37" t="inlineStr">
+        <is>
+          <t>High case</t>
+        </is>
+      </c>
+      <c r="C122" s="37" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D122" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E122" s="43" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F122" s="43" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G122" s="43" t="n">
+        <v>10600</v>
+      </c>
+      <c r="H122" s="43" t="n">
+        <v>17800</v>
+      </c>
+      <c r="I122" s="43" t="n">
+        <v>26800</v>
+      </c>
+      <c r="J122" s="43" t="n">
+        <v>37600</v>
+      </c>
+      <c r="K122" s="43" t="n">
+        <v>50200</v>
+      </c>
+      <c r="L122" s="43" t="n">
+        <v>64600</v>
+      </c>
+      <c r="M122" s="43" t="n">
+        <v>80800</v>
+      </c>
+      <c r="N122" s="43" t="n">
+        <v>98800</v>
+      </c>
+      <c r="O122" s="37" t="n"/>
+      <c r="P122" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q122" s="37" t="inlineStr">
+        <is>
+          <t>Forecast share x naamsa's sales outlook, added up</t>
+        </is>
+      </c>
+      <c r="R122" s="37" t="inlineStr"/>
+      <c r="S122" s="37" t="inlineStr">
+        <is>
+          <t>3.5% of today's light commercial fleet by 2035. Sales after 2027 are held at naamsa's 2027 projection; no electric vehicle is scrapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="42.5" customHeight="1">
+      <c r="A123" s="37" t="inlineStr">
+        <is>
+          <t>Petrol and diesel displaced by electric light commercial vehicles, forecast</t>
+        </is>
+      </c>
+      <c r="B123" s="37" t="inlineStr">
+        <is>
+          <t>Low case</t>
+        </is>
+      </c>
+      <c r="C123" s="37" t="inlineStr">
+        <is>
+          <t>million litres a year</t>
+        </is>
+      </c>
+      <c r="D123" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="37" t="n"/>
+      <c r="P123" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q123" s="37" t="inlineStr">
+        <is>
+          <t>Electric vehicles on the road x a light commercial vehicle's yearly fuel use (Stone et al. 2018)</t>
+        </is>
+      </c>
+      <c r="R123" s="37" t="inlineStr"/>
+      <c r="S123" s="37" t="inlineStr">
+        <is>
+          <t>Each electric vehicle is taken to replace an average light commercial vehicle. Delivery vans drive more than average, so the true figure is higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="42.5" customHeight="1">
+      <c r="A124" s="37" t="inlineStr">
+        <is>
+          <t>Petrol and diesel displaced by electric light commercial vehicles, forecast</t>
+        </is>
+      </c>
+      <c r="B124" s="37" t="inlineStr">
+        <is>
+          <t>Medium case</t>
+        </is>
+      </c>
+      <c r="C124" s="37" t="inlineStr">
+        <is>
+          <t>million litres a year</t>
+        </is>
+      </c>
+      <c r="D124" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E124" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G124" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="H124" s="43" t="n">
+        <v>9</v>
+      </c>
+      <c r="I124" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="J124" s="43" t="n">
+        <v>23</v>
+      </c>
+      <c r="K124" s="43" t="n">
         <v>35</v>
       </c>
-      <c r="K106" s="35" t="n"/>
-      <c r="L106" s="35" t="n"/>
-      <c r="M106" s="35" t="n"/>
-      <c r="N106" s="35" t="n"/>
-      <c r="O106" s="35" t="n"/>
-      <c r="P106" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q106" s="35" t="inlineStr">
-        <is>
-          <t>IEA, Fuel economy in South Africa (Global Fuel Economy Initiative 2021)</t>
-        </is>
-      </c>
-      <c r="R106" s="35" t="inlineStr"/>
-      <c r="S106" s="35" t="inlineStr">
-        <is>
-          <t>No later figure found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="42.5" customHeight="1">
-      <c r="A107" s="41" t="inlineStr">
-        <is>
-          <t>Electric trucks and electric light commercial vehicles sold</t>
-        </is>
-      </c>
-      <c r="B107" s="41" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C107" s="41" t="inlineStr">
+      <c r="L124" s="43" t="n">
+        <v>51</v>
+      </c>
+      <c r="M124" s="43" t="n">
+        <v>71</v>
+      </c>
+      <c r="N124" s="43" t="n">
+        <v>95</v>
+      </c>
+      <c r="O124" s="37" t="n"/>
+      <c r="P124" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q124" s="37" t="inlineStr">
+        <is>
+          <t>Electric vehicles on the road x a light commercial vehicle's yearly fuel use (Stone et al. 2018)</t>
+        </is>
+      </c>
+      <c r="R124" s="37" t="inlineStr"/>
+      <c r="S124" s="37" t="inlineStr">
+        <is>
+          <t>Each electric vehicle is taken to replace an average light commercial vehicle. Delivery vans drive more than average, so the true figure is higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="42.5" customHeight="1">
+      <c r="A125" s="37" t="inlineStr">
+        <is>
+          <t>Petrol and diesel displaced by electric light commercial vehicles, forecast</t>
+        </is>
+      </c>
+      <c r="B125" s="37" t="inlineStr">
+        <is>
+          <t>High case</t>
+        </is>
+      </c>
+      <c r="C125" s="37" t="inlineStr">
+        <is>
+          <t>million litres a year</t>
+        </is>
+      </c>
+      <c r="D125" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E125" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F125" s="43" t="n">
+        <v>14</v>
+      </c>
+      <c r="G125" s="43" t="n">
+        <v>28</v>
+      </c>
+      <c r="H125" s="43" t="n">
+        <v>47</v>
+      </c>
+      <c r="I125" s="43" t="n">
+        <v>71</v>
+      </c>
+      <c r="J125" s="43" t="n">
+        <v>99</v>
+      </c>
+      <c r="K125" s="43" t="n">
+        <v>132</v>
+      </c>
+      <c r="L125" s="43" t="n">
+        <v>170</v>
+      </c>
+      <c r="M125" s="43" t="n">
+        <v>213</v>
+      </c>
+      <c r="N125" s="43" t="n">
+        <v>260</v>
+      </c>
+      <c r="O125" s="37" t="n"/>
+      <c r="P125" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q125" s="37" t="inlineStr">
+        <is>
+          <t>Electric vehicles on the road x a light commercial vehicle's yearly fuel use (Stone et al. 2018)</t>
+        </is>
+      </c>
+      <c r="R125" s="37" t="inlineStr"/>
+      <c r="S125" s="37" t="inlineStr">
+        <is>
+          <t>Each electric vehicle is taken to replace an average light commercial vehicle. Delivery vans drive more than average, so the true figure is higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="34" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B126" s="34" t="inlineStr">
+        <is>
+          <t>Covers</t>
+        </is>
+      </c>
+      <c r="C126" s="34" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D126" s="34" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="E126" s="34" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="K126" s="34" t="n"/>
+      <c r="L126" s="34" t="n"/>
+      <c r="M126" s="34" t="n"/>
+      <c r="N126" s="34" t="n"/>
+      <c r="O126" s="34" t="n"/>
+      <c r="P126" s="34" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Q126" s="34" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="R126" s="34" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="S126" s="34" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15.5" customHeight="1">
+      <c r="A127" s="35" t="inlineStr">
+        <is>
+          <t>New vehicles sold, by segment</t>
+        </is>
+      </c>
+      <c r="B127" s="35" t="inlineStr">
+        <is>
+          <t>cars</t>
+        </is>
+      </c>
+      <c r="C127" s="35" t="inlineStr">
         <is>
           <t>vehicles</t>
         </is>
       </c>
-      <c r="D107" s="41" t="inlineStr"/>
-      <c r="E107" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="K107" s="41" t="n"/>
-      <c r="L107" s="41" t="n"/>
-      <c r="M107" s="41" t="n"/>
-      <c r="N107" s="41" t="n"/>
-      <c r="O107" s="41" t="n"/>
-      <c r="P107" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="Q107" s="41" t="inlineStr">
-        <is>
-          <t>None published</t>
-        </is>
-      </c>
-      <c r="R107" s="41" t="inlineStr"/>
-      <c r="S107" s="41" t="inlineStr">
-        <is>
-          <t>naamsa reports electric sales by drivetrain, not by segment (checked its fourth-quarter 2025 review). Benchmarks from other countries are on the HML response sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="33" t="inlineStr">
-        <is>
-          <t>Vehicle efficiency and distance</t>
-        </is>
-      </c>
-      <c r="B109" s="33" t="n"/>
-      <c r="C109" s="33" t="n"/>
-      <c r="D109" s="33" t="n"/>
-      <c r="E109" s="33" t="n"/>
-      <c r="F109" s="33" t="n"/>
-      <c r="G109" s="33" t="n"/>
-      <c r="H109" s="33" t="n"/>
-      <c r="I109" s="33" t="n"/>
-      <c r="J109" s="33" t="n"/>
-      <c r="K109" s="33" t="n"/>
-      <c r="L109" s="33" t="n"/>
-      <c r="M109" s="33" t="n"/>
-      <c r="N109" s="33" t="n"/>
-      <c r="O109" s="33" t="n"/>
-      <c r="P109" s="33" t="n"/>
-      <c r="Q109" s="33" t="n"/>
-      <c r="R109" s="33" t="n"/>
-      <c r="S109" s="33" t="n"/>
-      <c r="T109" s="33" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="34" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B110" s="34" t="inlineStr">
-        <is>
-          <t>Covers</t>
-        </is>
-      </c>
-      <c r="C110" s="34" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D110" s="34" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="E110" s="42" t="n">
-        <v>2005</v>
-      </c>
-      <c r="F110" s="42" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G110" s="42" t="n">
-        <v>2010</v>
-      </c>
-      <c r="H110" s="42" t="n">
-        <v>2011</v>
-      </c>
-      <c r="I110" s="42" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J110" s="42" t="n">
-        <v>2013</v>
-      </c>
-      <c r="K110" s="42" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L110" s="42" t="n">
-        <v>2015</v>
-      </c>
-      <c r="M110" s="42" t="n">
-        <v>2019</v>
-      </c>
-      <c r="N110" s="34" t="n"/>
-      <c r="O110" s="34" t="n"/>
-      <c r="P110" s="34" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="Q110" s="34" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="R110" s="34" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="S110" s="34" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="29" customHeight="1">
-      <c r="A111" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use of new light vehicles, by year</t>
-        </is>
-      </c>
-      <c r="B111" s="35" t="inlineStr">
-        <is>
-          <t>New cars and light commercial vehicles</t>
-        </is>
-      </c>
-      <c r="C111" s="35" t="inlineStr">
-        <is>
-          <t>litres of petrol equivalent per 100 km</t>
-        </is>
-      </c>
-      <c r="D111" s="35" t="inlineStr">
-        <is>
-          <t>calendar years</t>
-        </is>
-      </c>
-      <c r="E111" s="39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F111" s="39" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="G111" s="39" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H111" s="39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I111" s="39" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J111" s="39" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="K111" s="39" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L111" s="39" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M111" s="39" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N111" s="35" t="n"/>
-      <c r="O111" s="35" t="n"/>
-      <c r="P111" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q111" s="35" t="inlineStr">
-        <is>
-          <t>IEA and Global Fuel Economy Initiative (Working Paper 15, 2017; country page, 2021)</t>
-        </is>
-      </c>
-      <c r="R111" s="35" t="inlineStr">
-        <is>
-          <t>PDF p.119</t>
-        </is>
-      </c>
-      <c r="S111" s="35" t="inlineStr">
-        <is>
-          <t>Nothing after 2019 was found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="34" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B112" s="34" t="inlineStr">
-        <is>
-          <t>Covers</t>
-        </is>
-      </c>
-      <c r="C112" s="34" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D112" s="34" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="E112" s="34" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="K112" s="34" t="n"/>
-      <c r="L112" s="34" t="n"/>
-      <c r="M112" s="34" t="n"/>
-      <c r="N112" s="34" t="n"/>
-      <c r="O112" s="34" t="n"/>
-      <c r="P112" s="34" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="Q112" s="34" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="R112" s="34" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="S112" s="34" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="29" customHeight="1">
-      <c r="A113" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use and distance, petrol cars</t>
-        </is>
-      </c>
-      <c r="B113" s="35" t="inlineStr">
-        <is>
-          <t>fleet average</t>
-        </is>
-      </c>
-      <c r="C113" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km; km</t>
-        </is>
-      </c>
-      <c r="D113" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E113" s="44" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K113" s="35" t="n"/>
-      <c r="L113" s="35" t="n"/>
-      <c r="M113" s="35" t="n"/>
-      <c r="N113" s="35" t="n"/>
-      <c r="O113" s="35" t="n"/>
-      <c r="P113" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q113" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R113" s="35" t="inlineStr"/>
-      <c r="S113" s="35" t="inlineStr">
-        <is>
-          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="29" customHeight="1">
-      <c r="A114" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use and distance, petrol cars</t>
-        </is>
-      </c>
-      <c r="B114" s="35" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="C114" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km; km</t>
-        </is>
-      </c>
-      <c r="D114" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E114" s="44" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K114" s="35" t="n"/>
-      <c r="L114" s="35" t="n"/>
-      <c r="M114" s="35" t="n"/>
-      <c r="N114" s="35" t="n"/>
-      <c r="O114" s="35" t="n"/>
-      <c r="P114" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q114" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R114" s="35" t="inlineStr"/>
-      <c r="S114" s="35" t="inlineStr">
-        <is>
-          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="29" customHeight="1">
-      <c r="A115" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use and distance, petrol cars</t>
-        </is>
-      </c>
-      <c r="B115" s="35" t="inlineStr">
-        <is>
-          <t>km a year</t>
-        </is>
-      </c>
-      <c r="C115" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km; km</t>
-        </is>
-      </c>
-      <c r="D115" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E115" s="36" t="n">
-        <v>14457</v>
-      </c>
-      <c r="K115" s="35" t="n"/>
-      <c r="L115" s="35" t="n"/>
-      <c r="M115" s="35" t="n"/>
-      <c r="N115" s="35" t="n"/>
-      <c r="O115" s="35" t="n"/>
-      <c r="P115" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q115" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R115" s="35" t="inlineStr"/>
-      <c r="S115" s="35" t="inlineStr">
-        <is>
-          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="29" customHeight="1">
-      <c r="A116" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use and distance, diesel cars</t>
-        </is>
-      </c>
-      <c r="B116" s="35" t="inlineStr">
-        <is>
-          <t>fleet average</t>
-        </is>
-      </c>
-      <c r="C116" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km; km</t>
-        </is>
-      </c>
-      <c r="D116" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E116" s="44" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="K116" s="35" t="n"/>
-      <c r="L116" s="35" t="n"/>
-      <c r="M116" s="35" t="n"/>
-      <c r="N116" s="35" t="n"/>
-      <c r="O116" s="35" t="n"/>
-      <c r="P116" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q116" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R116" s="35" t="inlineStr"/>
-      <c r="S116" s="35" t="inlineStr">
-        <is>
-          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="29" customHeight="1">
-      <c r="A117" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use and distance, diesel cars</t>
-        </is>
-      </c>
-      <c r="B117" s="35" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="C117" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km; km</t>
-        </is>
-      </c>
-      <c r="D117" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E117" s="44" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K117" s="35" t="n"/>
-      <c r="L117" s="35" t="n"/>
-      <c r="M117" s="35" t="n"/>
-      <c r="N117" s="35" t="n"/>
-      <c r="O117" s="35" t="n"/>
-      <c r="P117" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q117" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R117" s="35" t="inlineStr"/>
-      <c r="S117" s="35" t="inlineStr">
-        <is>
-          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="29" customHeight="1">
-      <c r="A118" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use and distance, diesel cars</t>
-        </is>
-      </c>
-      <c r="B118" s="35" t="inlineStr">
-        <is>
-          <t>km a year</t>
-        </is>
-      </c>
-      <c r="C118" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km; km</t>
-        </is>
-      </c>
-      <c r="D118" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E118" s="36" t="n">
-        <v>16748</v>
-      </c>
-      <c r="K118" s="35" t="n"/>
-      <c r="L118" s="35" t="n"/>
-      <c r="M118" s="35" t="n"/>
-      <c r="N118" s="35" t="n"/>
-      <c r="O118" s="35" t="n"/>
-      <c r="P118" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q118" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R118" s="35" t="inlineStr"/>
-      <c r="S118" s="35" t="inlineStr">
-        <is>
-          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="29" customHeight="1">
-      <c r="A119" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use of new light vehicles: average change</t>
-        </is>
-      </c>
-      <c r="B119" s="35" t="inlineStr">
-        <is>
-          <t>New light-duty vehicles</t>
-        </is>
-      </c>
-      <c r="C119" s="35" t="inlineStr">
-        <is>
-          <t>% a year</t>
-        </is>
-      </c>
-      <c r="D119" s="35" t="inlineStr">
-        <is>
-          <t>2005-2019</t>
-        </is>
-      </c>
-      <c r="E119" s="44" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="K119" s="35" t="n"/>
-      <c r="L119" s="35" t="n"/>
-      <c r="M119" s="35" t="n"/>
-      <c r="N119" s="35" t="n"/>
-      <c r="O119" s="35" t="n"/>
-      <c r="P119" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q119" s="35" t="inlineStr">
-        <is>
-          <t>IEA, Fuel economy in South Africa (Global Fuel Economy Initiative 2021)</t>
-        </is>
-      </c>
-      <c r="R119" s="35" t="inlineStr"/>
-      <c r="S119" s="35" t="inlineStr">
-        <is>
-          <t>The model assumes 0.5 to 1.5% a year, so the observed rate sits inside the model's range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="29" customHeight="1">
-      <c r="A120" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use of new passenger cars</t>
-        </is>
-      </c>
-      <c r="B120" s="35" t="inlineStr">
-        <is>
-          <t>New passenger cars</t>
-        </is>
-      </c>
-      <c r="C120" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km</t>
-        </is>
-      </c>
-      <c r="D120" s="35" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="E120" s="44" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K120" s="35" t="n"/>
-      <c r="L120" s="35" t="n"/>
-      <c r="M120" s="35" t="n"/>
-      <c r="N120" s="35" t="n"/>
-      <c r="O120" s="35" t="n"/>
-      <c r="P120" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q120" s="35" t="inlineStr">
-        <is>
-          <t>ICCT white paper, South Africa's new passenger vehicle CO2 emission standards (January 2018)</t>
-        </is>
-      </c>
-      <c r="R120" s="35" t="inlineStr">
-        <is>
-          <t>PDF p.5</t>
-        </is>
-      </c>
-      <c r="S120" s="35" t="inlineStr">
-        <is>
-          <t>148 g CO2 per km on the older European test cycle, which reads lower than the worldwide cycle. From naamsa data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="29" customHeight="1">
-      <c r="A121" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use of trucks, lightest to heaviest class</t>
-        </is>
-      </c>
-      <c r="B121" s="35" t="inlineStr">
-        <is>
-          <t>Diesel trucks, class 1 of nine</t>
-        </is>
-      </c>
-      <c r="C121" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km, fleet average</t>
-        </is>
-      </c>
-      <c r="D121" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E121" s="44" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="K121" s="35" t="n"/>
-      <c r="L121" s="35" t="n"/>
-      <c r="M121" s="35" t="n"/>
-      <c r="N121" s="35" t="n"/>
-      <c r="O121" s="35" t="n"/>
-      <c r="P121" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q121" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R121" s="35" t="inlineStr"/>
-      <c r="S121" s="35" t="inlineStr">
-        <is>
-          <t>One year only. Light commercial diesel vehicles use 12.4 and buses 32.6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="29" customHeight="1">
-      <c r="A122" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use of trucks, lightest to heaviest class</t>
-        </is>
-      </c>
-      <c r="B122" s="35" t="inlineStr">
-        <is>
-          <t>Class 3</t>
-        </is>
-      </c>
-      <c r="C122" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km, fleet average</t>
-        </is>
-      </c>
-      <c r="D122" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E122" s="44" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="K122" s="35" t="n"/>
-      <c r="L122" s="35" t="n"/>
-      <c r="M122" s="35" t="n"/>
-      <c r="N122" s="35" t="n"/>
-      <c r="O122" s="35" t="n"/>
-      <c r="P122" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q122" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R122" s="35" t="inlineStr"/>
-      <c r="S122" s="35" t="inlineStr">
-        <is>
-          <t>One year only. Light commercial diesel vehicles use 12.4 and buses 32.6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="29" customHeight="1">
-      <c r="A123" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use of trucks, lightest to heaviest class</t>
-        </is>
-      </c>
-      <c r="B123" s="35" t="inlineStr">
-        <is>
-          <t>Class 6</t>
-        </is>
-      </c>
-      <c r="C123" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km, fleet average</t>
-        </is>
-      </c>
-      <c r="D123" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E123" s="44" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="K123" s="35" t="n"/>
-      <c r="L123" s="35" t="n"/>
-      <c r="M123" s="35" t="n"/>
-      <c r="N123" s="35" t="n"/>
-      <c r="O123" s="35" t="n"/>
-      <c r="P123" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q123" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R123" s="35" t="inlineStr"/>
-      <c r="S123" s="35" t="inlineStr">
-        <is>
-          <t>One year only. Light commercial diesel vehicles use 12.4 and buses 32.6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="29" customHeight="1">
-      <c r="A124" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use of trucks, lightest to heaviest class</t>
-        </is>
-      </c>
-      <c r="B124" s="35" t="inlineStr">
-        <is>
-          <t>Class 9</t>
-        </is>
-      </c>
-      <c r="C124" s="35" t="inlineStr">
-        <is>
-          <t>litres per 100 km, fleet average</t>
-        </is>
-      </c>
-      <c r="D124" s="35" t="inlineStr">
-        <is>
-          <t>2010 fleet</t>
-        </is>
-      </c>
-      <c r="E124" s="44" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="K124" s="35" t="n"/>
-      <c r="L124" s="35" t="n"/>
-      <c r="M124" s="35" t="n"/>
-      <c r="N124" s="35" t="n"/>
-      <c r="O124" s="35" t="n"/>
-      <c r="P124" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q124" s="35" t="inlineStr">
-        <is>
-          <t>Stone et al. (2018), vehicle parc model</t>
-        </is>
-      </c>
-      <c r="R124" s="35" t="inlineStr"/>
-      <c r="S124" s="35" t="inlineStr">
-        <is>
-          <t>One year only. Light commercial diesel vehicles use 12.4 and buses 32.6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="29" customHeight="1">
-      <c r="A125" s="35" t="inlineStr">
-        <is>
-          <t>Fuel use of new light vehicles: figure in use</t>
-        </is>
-      </c>
-      <c r="B125" s="35" t="inlineStr">
-        <is>
-          <t>New cars and light commercial vehicles</t>
-        </is>
-      </c>
-      <c r="C125" s="35" t="inlineStr">
-        <is>
-          <t>litres of petrol equivalent per 100 km</t>
-        </is>
-      </c>
-      <c r="D125" s="35" t="inlineStr">
-        <is>
-          <t>2019, used for later years</t>
-        </is>
-      </c>
-      <c r="E125" s="44" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K125" s="35" t="n"/>
-      <c r="L125" s="35" t="n"/>
-      <c r="M125" s="35" t="n"/>
-      <c r="N125" s="35" t="n"/>
-      <c r="O125" s="35" t="n"/>
-      <c r="P125" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q125" s="35" t="inlineStr">
-        <is>
-          <t>IEA, Fuel economy in South Africa (Global Fuel Economy Initiative 2021)</t>
-        </is>
-      </c>
-      <c r="R125" s="35" t="inlineStr"/>
-      <c r="S125" s="35" t="inlineStr">
-        <is>
-          <t>The latest published figure. Used as it stands for the years after 2019 (Manish, 8 October).</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="29" customHeight="1">
-      <c r="A126" s="41" t="inlineStr">
-        <is>
-          <t>Fuel use of trucks, by year</t>
-        </is>
-      </c>
-      <c r="B126" s="41" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C126" s="41" t="inlineStr">
-        <is>
-          <t>litres per 100 km</t>
-        </is>
-      </c>
-      <c r="D126" s="41" t="inlineStr"/>
-      <c r="E126" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="K126" s="41" t="n"/>
-      <c r="L126" s="41" t="n"/>
-      <c r="M126" s="41" t="n"/>
-      <c r="N126" s="41" t="n"/>
-      <c r="O126" s="41" t="n"/>
-      <c r="P126" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="Q126" s="41" t="inlineStr">
-        <is>
-          <t>None found</t>
-        </is>
-      </c>
-      <c r="R126" s="41" t="inlineStr"/>
-      <c r="S126" s="41" t="inlineStr">
-        <is>
-          <t>Only the 2010 fleet figures above exist. No truck series by year was found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="29" customHeight="1">
-      <c r="A127" s="35" t="inlineStr">
-        <is>
-          <t>Efficiency gain assumed in the model</t>
-        </is>
-      </c>
-      <c r="B127" s="35" t="inlineStr">
-        <is>
-          <t>New diesel vehicles, high demand case</t>
-        </is>
-      </c>
-      <c r="C127" s="35" t="inlineStr">
-        <is>
-          <t>% a year</t>
-        </is>
-      </c>
       <c r="D127" s="35" t="inlineStr">
         <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="E127" s="44" t="n">
-        <v>0.5</v>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E127" s="36" t="n">
+        <v>422463</v>
       </c>
       <c r="K127" s="35" t="n"/>
       <c r="L127" s="35" t="n"/>
@@ -23460,39 +23711,35 @@
       </c>
       <c r="Q127" s="35" t="inlineStr">
         <is>
-          <t>Reatile workbook (model input)</t>
+          <t>naamsa, industry vehicle sales</t>
         </is>
       </c>
       <c r="R127" s="35" t="inlineStr"/>
-      <c r="S127" s="35" t="inlineStr">
-        <is>
-          <t>A model setting with no source behind it. Nothing was found to confirm or replace it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="29" customHeight="1">
+      <c r="S127" s="35" t="inlineStr"/>
+    </row>
+    <row r="128" ht="15.5" customHeight="1">
       <c r="A128" s="35" t="inlineStr">
         <is>
-          <t>Efficiency gain assumed in the model</t>
+          <t>New vehicles sold, by segment</t>
         </is>
       </c>
       <c r="B128" s="35" t="inlineStr">
         <is>
-          <t>New diesel vehicles, low demand case</t>
+          <t>light commercial</t>
         </is>
       </c>
       <c r="C128" s="35" t="inlineStr">
         <is>
-          <t>% a year</t>
+          <t>vehicles</t>
         </is>
       </c>
       <c r="D128" s="35" t="inlineStr">
         <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="E128" s="44" t="n">
-        <v>1</v>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E128" s="36" t="n">
+        <v>143964</v>
       </c>
       <c r="K128" s="35" t="n"/>
       <c r="L128" s="35" t="n"/>
@@ -23506,39 +23753,35 @@
       </c>
       <c r="Q128" s="35" t="inlineStr">
         <is>
-          <t>Reatile workbook (model input)</t>
+          <t>naamsa, industry vehicle sales</t>
         </is>
       </c>
       <c r="R128" s="35" t="inlineStr"/>
-      <c r="S128" s="35" t="inlineStr">
-        <is>
-          <t>A model setting with no source behind it. Nothing was found to confirm or replace it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="29" customHeight="1">
+      <c r="S128" s="35" t="inlineStr"/>
+    </row>
+    <row r="129" ht="15.5" customHeight="1">
       <c r="A129" s="35" t="inlineStr">
         <is>
-          <t>Efficiency gain assumed in the model</t>
+          <t>New vehicles sold, by segment</t>
         </is>
       </c>
       <c r="B129" s="35" t="inlineStr">
         <is>
-          <t>New petrol vehicles, high demand case</t>
+          <t>medium and heavy commercial</t>
         </is>
       </c>
       <c r="C129" s="35" t="inlineStr">
         <is>
-          <t>% a year</t>
+          <t>vehicles</t>
         </is>
       </c>
       <c r="D129" s="35" t="inlineStr">
         <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="E129" s="44" t="n">
-        <v>1</v>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E129" s="36" t="n">
+        <v>30911</v>
       </c>
       <c r="K129" s="35" t="n"/>
       <c r="L129" s="35" t="n"/>
@@ -23552,39 +23795,35 @@
       </c>
       <c r="Q129" s="35" t="inlineStr">
         <is>
-          <t>Reatile workbook (model input)</t>
+          <t>naamsa, industry vehicle sales</t>
         </is>
       </c>
       <c r="R129" s="35" t="inlineStr"/>
-      <c r="S129" s="35" t="inlineStr">
-        <is>
-          <t>A model setting with no source behind it. Nothing was found to confirm or replace it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="29" customHeight="1">
+      <c r="S129" s="35" t="inlineStr"/>
+    </row>
+    <row r="130" ht="15.5" customHeight="1">
       <c r="A130" s="35" t="inlineStr">
         <is>
-          <t>Efficiency gain assumed in the model</t>
+          <t>Electric and hybrid vehicles sold</t>
         </is>
       </c>
       <c r="B130" s="35" t="inlineStr">
         <is>
-          <t>New petrol vehicles, low demand case</t>
+          <t>battery electric</t>
         </is>
       </c>
       <c r="C130" s="35" t="inlineStr">
         <is>
-          <t>% a year</t>
+          <t>vehicles</t>
         </is>
       </c>
       <c r="D130" s="35" t="inlineStr">
         <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="E130" s="44" t="n">
-        <v>1.5</v>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E130" s="36" t="n">
+        <v>1088</v>
       </c>
       <c r="K130" s="35" t="n"/>
       <c r="L130" s="35" t="n"/>
@@ -23598,621 +23837,567 @@
       </c>
       <c r="Q130" s="35" t="inlineStr">
         <is>
-          <t>Reatile workbook (model input)</t>
+          <t>naamsa, new energy vehicle sales</t>
         </is>
       </c>
       <c r="R130" s="35" t="inlineStr"/>
-      <c r="S130" s="35" t="inlineStr">
-        <is>
-          <t>A model setting with no source behind it. Nothing was found to confirm or replace it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="33" t="inlineStr">
-        <is>
-          <t>Freight and rail</t>
-        </is>
-      </c>
-      <c r="B132" s="33" t="n"/>
-      <c r="C132" s="33" t="n"/>
-      <c r="D132" s="33" t="n"/>
-      <c r="E132" s="33" t="n"/>
-      <c r="F132" s="33" t="n"/>
-      <c r="G132" s="33" t="n"/>
-      <c r="H132" s="33" t="n"/>
-      <c r="I132" s="33" t="n"/>
-      <c r="J132" s="33" t="n"/>
-      <c r="K132" s="33" t="n"/>
-      <c r="L132" s="33" t="n"/>
-      <c r="M132" s="33" t="n"/>
-      <c r="N132" s="33" t="n"/>
-      <c r="O132" s="33" t="n"/>
-      <c r="P132" s="33" t="n"/>
-      <c r="Q132" s="33" t="n"/>
-      <c r="R132" s="33" t="n"/>
-      <c r="S132" s="33" t="n"/>
-      <c r="T132" s="33" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="34" t="inlineStr">
+      <c r="S130" s="35" t="inlineStr"/>
+    </row>
+    <row r="131" ht="15.5" customHeight="1">
+      <c r="A131" s="35" t="inlineStr">
+        <is>
+          <t>Electric and hybrid vehicles sold</t>
+        </is>
+      </c>
+      <c r="B131" s="35" t="inlineStr">
+        <is>
+          <t>plug-in hybrid</t>
+        </is>
+      </c>
+      <c r="C131" s="35" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D131" s="35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E131" s="36" t="n">
+        <v>2810</v>
+      </c>
+      <c r="K131" s="35" t="n"/>
+      <c r="L131" s="35" t="n"/>
+      <c r="M131" s="35" t="n"/>
+      <c r="N131" s="35" t="n"/>
+      <c r="O131" s="35" t="n"/>
+      <c r="P131" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q131" s="35" t="inlineStr">
+        <is>
+          <t>naamsa, new energy vehicle sales</t>
+        </is>
+      </c>
+      <c r="R131" s="35" t="inlineStr"/>
+      <c r="S131" s="35" t="inlineStr"/>
+    </row>
+    <row r="132" ht="15.5" customHeight="1">
+      <c r="A132" s="35" t="inlineStr">
+        <is>
+          <t>Electric and hybrid vehicles sold</t>
+        </is>
+      </c>
+      <c r="B132" s="35" t="inlineStr">
+        <is>
+          <t>conventional hybrid</t>
+        </is>
+      </c>
+      <c r="C132" s="35" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D132" s="35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E132" s="36" t="n">
+        <v>12818</v>
+      </c>
+      <c r="K132" s="35" t="n"/>
+      <c r="L132" s="35" t="n"/>
+      <c r="M132" s="35" t="n"/>
+      <c r="N132" s="35" t="n"/>
+      <c r="O132" s="35" t="n"/>
+      <c r="P132" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q132" s="35" t="inlineStr">
+        <is>
+          <t>naamsa, new energy vehicle sales</t>
+        </is>
+      </c>
+      <c r="R132" s="35" t="inlineStr"/>
+      <c r="S132" s="35" t="inlineStr"/>
+    </row>
+    <row r="133" ht="15.5" customHeight="1">
+      <c r="A133" s="37" t="inlineStr">
+        <is>
+          <t>Share of new vehicles sold</t>
+        </is>
+      </c>
+      <c r="B133" s="37" t="inlineStr">
+        <is>
+          <t>battery electric</t>
+        </is>
+      </c>
+      <c r="C133" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D133" s="37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E133" s="38" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K133" s="37" t="n"/>
+      <c r="L133" s="37" t="n"/>
+      <c r="M133" s="37" t="n"/>
+      <c r="N133" s="37" t="n"/>
+      <c r="O133" s="37" t="n"/>
+      <c r="P133" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q133" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the two naamsa series</t>
+        </is>
+      </c>
+      <c r="R133" s="37" t="inlineStr"/>
+      <c r="S133" s="37" t="inlineStr">
+        <is>
+          <t>Battery electric sales fell from 2024 to 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="15.5" customHeight="1">
+      <c r="A134" s="37" t="inlineStr">
+        <is>
+          <t>Share of new vehicles sold</t>
+        </is>
+      </c>
+      <c r="B134" s="37" t="inlineStr">
+        <is>
+          <t>plug-in hybrid</t>
+        </is>
+      </c>
+      <c r="C134" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D134" s="37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E134" s="38" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="K134" s="37" t="n"/>
+      <c r="L134" s="37" t="n"/>
+      <c r="M134" s="37" t="n"/>
+      <c r="N134" s="37" t="n"/>
+      <c r="O134" s="37" t="n"/>
+      <c r="P134" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q134" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the two naamsa series</t>
+        </is>
+      </c>
+      <c r="R134" s="37" t="inlineStr"/>
+      <c r="S134" s="37" t="inlineStr">
+        <is>
+          <t>Battery electric sales fell from 2024 to 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="15.5" customHeight="1">
+      <c r="A135" s="37" t="inlineStr">
+        <is>
+          <t>Share of new vehicles sold</t>
+        </is>
+      </c>
+      <c r="B135" s="37" t="inlineStr">
+        <is>
+          <t>conventional hybrid</t>
+        </is>
+      </c>
+      <c r="C135" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D135" s="37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E135" s="38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K135" s="37" t="n"/>
+      <c r="L135" s="37" t="n"/>
+      <c r="M135" s="37" t="n"/>
+      <c r="N135" s="37" t="n"/>
+      <c r="O135" s="37" t="n"/>
+      <c r="P135" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q135" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the two naamsa series</t>
+        </is>
+      </c>
+      <c r="R135" s="37" t="inlineStr"/>
+      <c r="S135" s="37" t="inlineStr">
+        <is>
+          <t>Battery electric sales fell from 2024 to 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="29" customHeight="1">
+      <c r="A136" s="35" t="inlineStr">
+        <is>
+          <t>Diesel share of new light vehicles sold</t>
+        </is>
+      </c>
+      <c r="B136" s="35" t="inlineStr">
+        <is>
+          <t>New light-duty vehicles</t>
+        </is>
+      </c>
+      <c r="C136" s="35" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D136" s="35" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="E136" s="36" t="n">
+        <v>35</v>
+      </c>
+      <c r="K136" s="35" t="n"/>
+      <c r="L136" s="35" t="n"/>
+      <c r="M136" s="35" t="n"/>
+      <c r="N136" s="35" t="n"/>
+      <c r="O136" s="35" t="n"/>
+      <c r="P136" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q136" s="35" t="inlineStr">
+        <is>
+          <t>IEA, Fuel economy in South Africa (Global Fuel Economy Initiative 2021)</t>
+        </is>
+      </c>
+      <c r="R136" s="35" t="inlineStr"/>
+      <c r="S136" s="35" t="inlineStr">
+        <is>
+          <t>No later figure found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="42.5" customHeight="1">
+      <c r="A137" s="41" t="inlineStr">
+        <is>
+          <t>Electric trucks and electric light commercial vehicles sold</t>
+        </is>
+      </c>
+      <c r="B137" s="41" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C137" s="41" t="inlineStr">
+        <is>
+          <t>vehicles</t>
+        </is>
+      </c>
+      <c r="D137" s="41" t="inlineStr"/>
+      <c r="E137" s="41" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="K137" s="41" t="n"/>
+      <c r="L137" s="41" t="n"/>
+      <c r="M137" s="41" t="n"/>
+      <c r="N137" s="41" t="n"/>
+      <c r="O137" s="41" t="n"/>
+      <c r="P137" s="41" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q137" s="41" t="inlineStr">
+        <is>
+          <t>None published</t>
+        </is>
+      </c>
+      <c r="R137" s="41" t="inlineStr"/>
+      <c r="S137" s="41" t="inlineStr">
+        <is>
+          <t>naamsa reports electric sales by drivetrain, not by segment (checked its fourth-quarter 2025 review). Benchmarks from other countries are on the HML response sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="33" t="inlineStr">
+        <is>
+          <t>Vehicle efficiency and distance</t>
+        </is>
+      </c>
+      <c r="B139" s="33" t="n"/>
+      <c r="C139" s="33" t="n"/>
+      <c r="D139" s="33" t="n"/>
+      <c r="E139" s="33" t="n"/>
+      <c r="F139" s="33" t="n"/>
+      <c r="G139" s="33" t="n"/>
+      <c r="H139" s="33" t="n"/>
+      <c r="I139" s="33" t="n"/>
+      <c r="J139" s="33" t="n"/>
+      <c r="K139" s="33" t="n"/>
+      <c r="L139" s="33" t="n"/>
+      <c r="M139" s="33" t="n"/>
+      <c r="N139" s="33" t="n"/>
+      <c r="O139" s="33" t="n"/>
+      <c r="P139" s="33" t="n"/>
+      <c r="Q139" s="33" t="n"/>
+      <c r="R139" s="33" t="n"/>
+      <c r="S139" s="33" t="n"/>
+      <c r="T139" s="33" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="34" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B133" s="34" t="inlineStr">
+      <c r="B140" s="34" t="inlineStr">
         <is>
           <t>Covers</t>
         </is>
       </c>
-      <c r="C133" s="34" t="inlineStr">
+      <c r="C140" s="34" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D133" s="34" t="inlineStr">
+      <c r="D140" s="34" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E133" s="42" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F133" s="42" t="n">
+      <c r="E140" s="42" t="n">
+        <v>2005</v>
+      </c>
+      <c r="F140" s="42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="G140" s="42" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H140" s="42" t="n">
+        <v>2011</v>
+      </c>
+      <c r="I140" s="42" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J140" s="42" t="n">
+        <v>2013</v>
+      </c>
+      <c r="K140" s="42" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L140" s="42" t="n">
+        <v>2015</v>
+      </c>
+      <c r="M140" s="42" t="n">
         <v>2019</v>
       </c>
-      <c r="G133" s="42" t="n">
-        <v>2020</v>
-      </c>
-      <c r="H133" s="42" t="n">
-        <v>2021</v>
-      </c>
-      <c r="I133" s="42" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J133" s="42" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K133" s="42" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L133" s="42" t="n">
-        <v>2025</v>
-      </c>
-      <c r="M133" s="34" t="n"/>
-      <c r="N133" s="34" t="n"/>
-      <c r="O133" s="34" t="n"/>
-      <c r="P133" s="34" t="inlineStr">
+      <c r="N140" s="34" t="n"/>
+      <c r="O140" s="34" t="n"/>
+      <c r="P140" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q133" s="34" t="inlineStr">
+      <c r="Q140" s="34" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="R133" s="34" t="inlineStr">
+      <c r="R140" s="34" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="S133" s="34" t="inlineStr">
+      <c r="S140" s="34" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="29" customHeight="1">
-      <c r="A134" s="35" t="inlineStr">
-        <is>
-          <t>Freight carried by road</t>
-        </is>
-      </c>
-      <c r="B134" s="35" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C134" s="35" t="inlineStr">
-        <is>
-          <t>million tonnes</t>
-        </is>
-      </c>
-      <c r="D134" s="35" t="inlineStr">
+    <row r="141" ht="29" customHeight="1">
+      <c r="A141" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use of new light vehicles, by year</t>
+        </is>
+      </c>
+      <c r="B141" s="35" t="inlineStr">
+        <is>
+          <t>New cars and light commercial vehicles</t>
+        </is>
+      </c>
+      <c r="C141" s="35" t="inlineStr">
+        <is>
+          <t>litres of petrol equivalent per 100 km</t>
+        </is>
+      </c>
+      <c r="D141" s="35" t="inlineStr">
         <is>
           <t>calendar years</t>
         </is>
       </c>
-      <c r="E134" s="35" t="n"/>
-      <c r="F134" s="35" t="n"/>
-      <c r="G134" s="35" t="n"/>
-      <c r="H134" s="35" t="n"/>
-      <c r="I134" s="35" t="n"/>
-      <c r="J134" s="35" t="n"/>
-      <c r="K134" s="61" t="n">
-        <v>980</v>
-      </c>
-      <c r="L134" s="61" t="n">
-        <v>976</v>
-      </c>
-      <c r="M134" s="35" t="n"/>
-      <c r="N134" s="35" t="n"/>
-      <c r="O134" s="35" t="n"/>
-      <c r="P134" s="35" t="inlineStr">
+      <c r="E141" s="39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F141" s="39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G141" s="39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H141" s="39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I141" s="39" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J141" s="39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K141" s="39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L141" s="39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M141" s="39" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N141" s="35" t="n"/>
+      <c r="O141" s="35" t="n"/>
+      <c r="P141" s="35" t="inlineStr">
         <is>
           <t>From source</t>
         </is>
       </c>
-      <c r="Q134" s="35" t="inlineStr">
-        <is>
-          <t>Statistics South Africa, Land transport survey (P7162), December 2025</t>
-        </is>
-      </c>
-      <c r="R134" s="35" t="inlineStr">
-        <is>
-          <t>PDF p.7</t>
-        </is>
-      </c>
-      <c r="S134" s="35" t="inlineStr">
-        <is>
-          <t>Tonnes, not tonne-kilometres.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="29" customHeight="1">
-      <c r="A135" s="35" t="inlineStr">
-        <is>
-          <t>Freight carried by rail</t>
-        </is>
-      </c>
-      <c r="B135" s="35" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C135" s="35" t="inlineStr">
-        <is>
-          <t>million tonnes</t>
-        </is>
-      </c>
-      <c r="D135" s="35" t="inlineStr">
-        <is>
-          <t>calendar years</t>
-        </is>
-      </c>
-      <c r="E135" s="35" t="n"/>
-      <c r="F135" s="35" t="n"/>
-      <c r="G135" s="35" t="n"/>
-      <c r="H135" s="35" t="n"/>
-      <c r="I135" s="35" t="n"/>
-      <c r="J135" s="35" t="n"/>
-      <c r="K135" s="61" t="n">
-        <v>161</v>
-      </c>
-      <c r="L135" s="61" t="n">
-        <v>168</v>
-      </c>
-      <c r="M135" s="35" t="n"/>
-      <c r="N135" s="35" t="n"/>
-      <c r="O135" s="35" t="n"/>
-      <c r="P135" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q135" s="35" t="inlineStr">
-        <is>
-          <t>Statistics South Africa, Land transport survey (P7162), December 2025</t>
-        </is>
-      </c>
-      <c r="R135" s="35" t="inlineStr">
-        <is>
-          <t>PDF p.7</t>
-        </is>
-      </c>
-      <c r="S135" s="35" t="inlineStr">
-        <is>
-          <t>Tonnes, not tonne-kilometres.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="15.5" customHeight="1">
-      <c r="A136" s="37" t="inlineStr">
-        <is>
-          <t>Rail's share of road and rail tonnes</t>
-        </is>
-      </c>
-      <c r="B136" s="37" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C136" s="37" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D136" s="37" t="inlineStr">
-        <is>
-          <t>calendar years</t>
-        </is>
-      </c>
-      <c r="E136" s="37" t="n"/>
-      <c r="F136" s="37" t="n"/>
-      <c r="G136" s="37" t="n"/>
-      <c r="H136" s="37" t="n"/>
-      <c r="I136" s="37" t="n"/>
-      <c r="J136" s="37" t="n"/>
-      <c r="K136" s="40" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="L136" s="40" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M136" s="37" t="n"/>
-      <c r="N136" s="37" t="n"/>
-      <c r="O136" s="37" t="n"/>
-      <c r="P136" s="37" t="inlineStr">
-        <is>
-          <t>Calculated</t>
-        </is>
-      </c>
-      <c r="Q136" s="37" t="inlineStr">
-        <is>
-          <t>Calculated from the survey</t>
-        </is>
-      </c>
-      <c r="R136" s="37" t="inlineStr"/>
-      <c r="S136" s="37" t="inlineStr"/>
-    </row>
-    <row r="137" ht="29" customHeight="1">
-      <c r="A137" s="35" t="inlineStr">
-        <is>
-          <t>Freight carried by Transnet Freight Rail</t>
-        </is>
-      </c>
-      <c r="B137" s="35" t="inlineStr">
-        <is>
-          <t>Transnet Freight Rail, all freight</t>
-        </is>
-      </c>
-      <c r="C137" s="35" t="inlineStr">
-        <is>
-          <t>million tonnes</t>
-        </is>
-      </c>
-      <c r="D137" s="35" t="inlineStr">
-        <is>
-          <t>years to March</t>
-        </is>
-      </c>
-      <c r="E137" s="60" t="n">
-        <v>226.3</v>
-      </c>
-      <c r="F137" s="60" t="n">
-        <v>215.1</v>
-      </c>
-      <c r="G137" s="60" t="n">
-        <v>212.4</v>
-      </c>
-      <c r="H137" s="60" t="n">
-        <v>183.3</v>
-      </c>
-      <c r="I137" s="60" t="n">
-        <v>173.1</v>
-      </c>
-      <c r="J137" s="60" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="K137" s="60" t="n">
-        <v>151.7</v>
-      </c>
-      <c r="L137" s="60" t="n">
-        <v>160.1</v>
-      </c>
-      <c r="M137" s="35" t="n"/>
-      <c r="N137" s="35" t="n"/>
-      <c r="O137" s="35" t="n"/>
-      <c r="P137" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q137" s="35" t="inlineStr">
-        <is>
-          <t>Transnet annual results 2025, presentation</t>
-        </is>
-      </c>
-      <c r="R137" s="35" t="inlineStr">
-        <is>
-          <t>PDF p.14</t>
-        </is>
-      </c>
-      <c r="S137" s="35" t="inlineStr">
-        <is>
-          <t>Fell by a third from 2018 to 2023 and has risen since. Export iron ore, export coal and general freight together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="15.5" customHeight="1">
-      <c r="A138" s="35" t="inlineStr">
-        <is>
-          <t>Fuel used by Transnet, all divisions</t>
-        </is>
-      </c>
-      <c r="B138" s="35" t="inlineStr">
-        <is>
-          <t>Transnet, all divisions</t>
-        </is>
-      </c>
-      <c r="C138" s="35" t="inlineStr">
-        <is>
-          <t>million litres</t>
-        </is>
-      </c>
-      <c r="D138" s="35" t="inlineStr">
-        <is>
-          <t>years to March</t>
-        </is>
-      </c>
-      <c r="E138" s="35" t="n"/>
-      <c r="F138" s="35" t="n"/>
-      <c r="G138" s="35" t="n"/>
-      <c r="H138" s="35" t="n"/>
-      <c r="I138" s="35" t="n"/>
-      <c r="J138" s="35" t="n"/>
-      <c r="K138" s="61" t="n">
-        <v>190</v>
-      </c>
-      <c r="L138" s="61" t="n">
-        <v>199</v>
-      </c>
-      <c r="M138" s="35" t="n"/>
-      <c r="N138" s="35" t="n"/>
-      <c r="O138" s="35" t="n"/>
-      <c r="P138" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q138" s="35" t="inlineStr">
-        <is>
-          <t>Transnet Integrated Report 2025</t>
-        </is>
-      </c>
-      <c r="R138" s="35" t="inlineStr">
-        <is>
-          <t>PDF p.73</t>
-        </is>
-      </c>
-      <c r="S138" s="35" t="inlineStr">
-        <is>
-          <t>Up 4.37%, mainly an 8.49% rise in fuel for traction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="34" t="inlineStr">
+      <c r="Q141" s="35" t="inlineStr">
+        <is>
+          <t>IEA and Global Fuel Economy Initiative (Working Paper 15, 2017; country page, 2021)</t>
+        </is>
+      </c>
+      <c r="R141" s="35" t="inlineStr">
+        <is>
+          <t>PDF p.119</t>
+        </is>
+      </c>
+      <c r="S141" s="35" t="inlineStr">
+        <is>
+          <t>Nothing after 2019 was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="34" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B139" s="34" t="inlineStr">
+      <c r="B142" s="34" t="inlineStr">
         <is>
           <t>Covers</t>
         </is>
       </c>
-      <c r="C139" s="34" t="inlineStr">
+      <c r="C142" s="34" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D139" s="34" t="inlineStr">
+      <c r="D142" s="34" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="E139" s="34" t="inlineStr">
+      <c r="E142" s="34" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="K139" s="34" t="n"/>
-      <c r="L139" s="34" t="n"/>
-      <c r="M139" s="34" t="n"/>
-      <c r="N139" s="34" t="n"/>
-      <c r="O139" s="34" t="n"/>
-      <c r="P139" s="34" t="inlineStr">
+      <c r="K142" s="34" t="n"/>
+      <c r="L142" s="34" t="n"/>
+      <c r="M142" s="34" t="n"/>
+      <c r="N142" s="34" t="n"/>
+      <c r="O142" s="34" t="n"/>
+      <c r="P142" s="34" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q139" s="34" t="inlineStr">
+      <c r="Q142" s="34" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="R139" s="34" t="inlineStr">
+      <c r="R142" s="34" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
       </c>
-      <c r="S139" s="34" t="inlineStr">
+      <c r="S142" s="34" t="inlineStr">
         <is>
           <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="29" customHeight="1">
-      <c r="A140" s="35" t="inlineStr">
-        <is>
-          <t>Transnet's rail target</t>
-        </is>
-      </c>
-      <c r="B140" s="35" t="inlineStr">
-        <is>
-          <t>Transnet</t>
-        </is>
-      </c>
-      <c r="C140" s="35" t="inlineStr">
-        <is>
-          <t>million tonnes</t>
-        </is>
-      </c>
-      <c r="D140" s="35" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E140" s="36" t="n">
-        <v>250</v>
-      </c>
-      <c r="K140" s="35" t="n"/>
-      <c r="L140" s="35" t="n"/>
-      <c r="M140" s="35" t="n"/>
-      <c r="N140" s="35" t="n"/>
-      <c r="O140" s="35" t="n"/>
-      <c r="P140" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q140" s="35" t="inlineStr">
-        <is>
-          <t>Transnet annual results 2025, presentation</t>
-        </is>
-      </c>
-      <c r="R140" s="35" t="inlineStr">
-        <is>
-          <t>PDF p.36</t>
-        </is>
-      </c>
-      <c r="S140" s="35" t="inlineStr">
-        <is>
-          <t>Transnet 'aims to grow its capacity to handle 250 million tons'. The slide gives no year; Nigel cited 2030.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="29" customHeight="1">
-      <c r="A141" s="37" t="inlineStr">
-        <is>
-          <t>Extra rail freight if the target is met</t>
-        </is>
-      </c>
-      <c r="B141" s="37" t="inlineStr">
-        <is>
-          <t>Transnet Freight Rail</t>
-        </is>
-      </c>
-      <c r="C141" s="37" t="inlineStr">
-        <is>
-          <t>million tonnes</t>
-        </is>
-      </c>
-      <c r="D141" s="37" t="inlineStr">
-        <is>
-          <t>target less the year to March 2025</t>
-        </is>
-      </c>
-      <c r="E141" s="62" t="n">
-        <v>90</v>
-      </c>
-      <c r="K141" s="37" t="n"/>
-      <c r="L141" s="37" t="n"/>
-      <c r="M141" s="37" t="n"/>
-      <c r="N141" s="37" t="n"/>
-      <c r="O141" s="37" t="n"/>
-      <c r="P141" s="37" t="inlineStr">
-        <is>
-          <t>Calculated</t>
-        </is>
-      </c>
-      <c r="Q141" s="37" t="inlineStr">
-        <is>
-          <t>Calculated from the two rows above</t>
-        </is>
-      </c>
-      <c r="R141" s="37" t="inlineStr"/>
-      <c r="S141" s="37" t="inlineStr">
-        <is>
-          <t>About 9% of road freight tonnes. Not all of it would come from road.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="29" customHeight="1">
-      <c r="A142" s="35" t="inlineStr">
-        <is>
-          <t>Freight in tonne-kilometres</t>
-        </is>
-      </c>
-      <c r="B142" s="35" t="inlineStr">
-        <is>
-          <t>All freight</t>
-        </is>
-      </c>
-      <c r="C142" s="35" t="inlineStr">
-        <is>
-          <t>billion tonne-km</t>
-        </is>
-      </c>
-      <c r="D142" s="35" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="E142" s="36" t="n">
-        <v>446</v>
-      </c>
-      <c r="K142" s="35" t="n"/>
-      <c r="L142" s="35" t="n"/>
-      <c r="M142" s="35" t="n"/>
-      <c r="N142" s="35" t="n"/>
-      <c r="O142" s="35" t="n"/>
-      <c r="P142" s="35" t="inlineStr">
-        <is>
-          <t>From source</t>
-        </is>
-      </c>
-      <c r="Q142" s="35" t="inlineStr">
-        <is>
-          <t>Havenga et al., A proposed freight and passenger road-to-rail strategy for South Africa (SA-TIED)</t>
-        </is>
-      </c>
-      <c r="R142" s="35" t="inlineStr">
-        <is>
-          <t>PDF pp.17, 25</t>
-        </is>
-      </c>
-      <c r="S142" s="35" t="inlineStr">
-        <is>
-          <t>Line haul 305, last mile 132, pipelines and conveyors 9.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="29" customHeight="1">
       <c r="A143" s="35" t="inlineStr">
         <is>
-          <t>Freight in tonne-kilometres</t>
+          <t>Fuel use and distance, petrol cars</t>
         </is>
       </c>
       <c r="B143" s="35" t="inlineStr">
         <is>
-          <t>rail-friendly freight</t>
+          <t>fleet average</t>
         </is>
       </c>
       <c r="C143" s="35" t="inlineStr">
         <is>
-          <t>billion tonne-km</t>
+          <t>litres per 100 km; km</t>
         </is>
       </c>
       <c r="D143" s="35" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="E143" s="36" t="n">
-        <v>181</v>
+          <t>2010 fleet</t>
+        </is>
+      </c>
+      <c r="E143" s="44" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="K143" s="35" t="n"/>
       <c r="L143" s="35" t="n"/>
@@ -24226,43 +24411,39 @@
       </c>
       <c r="Q143" s="35" t="inlineStr">
         <is>
-          <t>Havenga et al., A proposed freight and passenger road-to-rail strategy for South Africa (SA-TIED)</t>
-        </is>
-      </c>
-      <c r="R143" s="35" t="inlineStr">
-        <is>
-          <t>PDF pp.17, 25</t>
-        </is>
-      </c>
+          <t>Stone et al. (2018), vehicle parc model</t>
+        </is>
+      </c>
+      <c r="R143" s="35" t="inlineStr"/>
       <c r="S143" s="35" t="inlineStr">
         <is>
-          <t>Line haul 305, last mile 132, pipelines and conveyors 9.</t>
+          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
         </is>
       </c>
     </row>
     <row r="144" ht="29" customHeight="1">
       <c r="A144" s="35" t="inlineStr">
         <is>
-          <t>Freight in tonne-kilometres</t>
+          <t>Fuel use and distance, petrol cars</t>
         </is>
       </c>
       <c r="B144" s="35" t="inlineStr">
         <is>
-          <t>carried by rail</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C144" s="35" t="inlineStr">
         <is>
-          <t>billion tonne-km</t>
+          <t>litres per 100 km; km</t>
         </is>
       </c>
       <c r="D144" s="35" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="E144" s="36" t="n">
-        <v>141</v>
+          <t>2010 fleet</t>
+        </is>
+      </c>
+      <c r="E144" s="44" t="n">
+        <v>7.8</v>
       </c>
       <c r="K144" s="35" t="n"/>
       <c r="L144" s="35" t="n"/>
@@ -24276,43 +24457,39 @@
       </c>
       <c r="Q144" s="35" t="inlineStr">
         <is>
-          <t>Havenga et al., A proposed freight and passenger road-to-rail strategy for South Africa (SA-TIED)</t>
-        </is>
-      </c>
-      <c r="R144" s="35" t="inlineStr">
-        <is>
-          <t>PDF pp.17, 25</t>
-        </is>
-      </c>
+          <t>Stone et al. (2018), vehicle parc model</t>
+        </is>
+      </c>
+      <c r="R144" s="35" t="inlineStr"/>
       <c r="S144" s="35" t="inlineStr">
         <is>
-          <t>Line haul 305, last mile 132, pipelines and conveyors 9.</t>
+          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="29" customHeight="1">
       <c r="A145" s="35" t="inlineStr">
         <is>
-          <t>General freight that rail should carry but does not</t>
+          <t>Fuel use and distance, petrol cars</t>
         </is>
       </c>
       <c r="B145" s="35" t="inlineStr">
         <is>
-          <t>Rail-friendly general freight on road</t>
+          <t>km a year</t>
         </is>
       </c>
       <c r="C145" s="35" t="inlineStr">
         <is>
-          <t>billion tonne-km</t>
+          <t>litres per 100 km; km</t>
         </is>
       </c>
       <c r="D145" s="35" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2010 fleet</t>
         </is>
       </c>
       <c r="E145" s="36" t="n">
-        <v>30</v>
+        <v>14457</v>
       </c>
       <c r="K145" s="35" t="n"/>
       <c r="L145" s="35" t="n"/>
@@ -24326,213 +24503,273 @@
       </c>
       <c r="Q145" s="35" t="inlineStr">
         <is>
-          <t>Havenga et al., A proposed freight and passenger road-to-rail strategy for South Africa (SA-TIED)</t>
-        </is>
-      </c>
-      <c r="R145" s="35" t="inlineStr">
-        <is>
-          <t>PDF p.26</t>
-        </is>
-      </c>
+          <t>Stone et al. (2018), vehicle parc model</t>
+        </is>
+      </c>
+      <c r="R145" s="35" t="inlineStr"/>
       <c r="S145" s="35" t="inlineStr">
         <is>
-          <t>As the source states it: rail should have carried 47 and carried 18. This is the freight that a road-to-rail shift would move.</t>
+          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
         </is>
       </c>
     </row>
     <row r="146" ht="29" customHeight="1">
-      <c r="A146" s="41" t="inlineStr">
-        <is>
-          <t>Road freight in tonne-kilometres, by year</t>
-        </is>
-      </c>
-      <c r="B146" s="41" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C146" s="41" t="inlineStr">
-        <is>
-          <t>billion tonne-km</t>
-        </is>
-      </c>
-      <c r="D146" s="41" t="inlineStr"/>
-      <c r="E146" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="K146" s="41" t="n"/>
-      <c r="L146" s="41" t="n"/>
-      <c r="M146" s="41" t="n"/>
-      <c r="N146" s="41" t="n"/>
-      <c r="O146" s="41" t="n"/>
-      <c r="P146" s="41" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="Q146" s="41" t="inlineStr">
-        <is>
-          <t>None published as numbers</t>
-        </is>
-      </c>
-      <c r="R146" s="41" t="inlineStr"/>
-      <c r="S146" s="41" t="inlineStr">
-        <is>
-          <t>The research group that models it (GAIN, Stellenbosch) shows yearly charts but publishes figures for single years only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="42.5" customHeight="1">
-      <c r="A147" s="37" t="inlineStr">
-        <is>
-          <t>Diesel used by rail locomotives</t>
-        </is>
-      </c>
-      <c r="B147" s="37" t="inlineStr">
-        <is>
-          <t>Transnet Freight Rail</t>
-        </is>
-      </c>
-      <c r="C147" s="37" t="inlineStr">
-        <is>
-          <t>million litres</t>
-        </is>
-      </c>
-      <c r="D147" s="37" t="inlineStr">
-        <is>
-          <t>year to March 2025</t>
-        </is>
-      </c>
-      <c r="E147" s="62" t="n">
-        <v>138</v>
-      </c>
-      <c r="K147" s="37" t="n"/>
-      <c r="L147" s="37" t="n"/>
-      <c r="M147" s="37" t="n"/>
-      <c r="N147" s="37" t="n"/>
-      <c r="O147" s="37" t="n"/>
-      <c r="P147" s="37" t="inlineStr">
-        <is>
-          <t>Calculated</t>
-        </is>
-      </c>
-      <c r="Q147" s="37" t="inlineStr">
-        <is>
-          <t>199 million litres x 69.2% used for diesel traction (both from the Transnet report)</t>
-        </is>
-      </c>
-      <c r="R147" s="37" t="inlineStr">
-        <is>
-          <t>PDF p.73</t>
-        </is>
-      </c>
-      <c r="S147" s="37" t="inlineStr">
-        <is>
-          <t>About 1% of diesel sales. So freight moving to rail saves nearly all the road diesel it displaces. The rest is generators 13.8%, vehicle fleets 10.2%, marine diesel 6.7%, jet fuel 0.1%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="33" t="inlineStr">
-        <is>
-          <t>Sector activity</t>
-        </is>
-      </c>
-      <c r="B149" s="33" t="n"/>
-      <c r="C149" s="33" t="n"/>
-      <c r="D149" s="33" t="n"/>
-      <c r="E149" s="33" t="n"/>
-      <c r="F149" s="33" t="n"/>
-      <c r="G149" s="33" t="n"/>
-      <c r="H149" s="33" t="n"/>
-      <c r="I149" s="33" t="n"/>
-      <c r="J149" s="33" t="n"/>
-      <c r="K149" s="33" t="n"/>
-      <c r="L149" s="33" t="n"/>
-      <c r="M149" s="33" t="n"/>
-      <c r="N149" s="33" t="n"/>
-      <c r="O149" s="33" t="n"/>
-      <c r="P149" s="33" t="n"/>
-      <c r="Q149" s="33" t="n"/>
-      <c r="R149" s="33" t="n"/>
-      <c r="S149" s="33" t="n"/>
-      <c r="T149" s="33" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="34" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B150" s="34" t="inlineStr">
-        <is>
-          <t>Covers</t>
-        </is>
-      </c>
-      <c r="C150" s="34" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D150" s="34" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="E150" s="34" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="K150" s="34" t="n"/>
-      <c r="L150" s="34" t="n"/>
-      <c r="M150" s="34" t="n"/>
-      <c r="N150" s="34" t="n"/>
-      <c r="O150" s="34" t="n"/>
-      <c r="P150" s="34" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="Q150" s="34" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="R150" s="34" t="inlineStr">
-        <is>
-          <t>Page</t>
-        </is>
-      </c>
-      <c r="S150" s="34" t="inlineStr">
-        <is>
-          <t>Note</t>
+      <c r="A146" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use and distance, diesel cars</t>
+        </is>
+      </c>
+      <c r="B146" s="35" t="inlineStr">
+        <is>
+          <t>fleet average</t>
+        </is>
+      </c>
+      <c r="C146" s="35" t="inlineStr">
+        <is>
+          <t>litres per 100 km; km</t>
+        </is>
+      </c>
+      <c r="D146" s="35" t="inlineStr">
+        <is>
+          <t>2010 fleet</t>
+        </is>
+      </c>
+      <c r="E146" s="44" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K146" s="35" t="n"/>
+      <c r="L146" s="35" t="n"/>
+      <c r="M146" s="35" t="n"/>
+      <c r="N146" s="35" t="n"/>
+      <c r="O146" s="35" t="n"/>
+      <c r="P146" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q146" s="35" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018), vehicle parc model</t>
+        </is>
+      </c>
+      <c r="R146" s="35" t="inlineStr"/>
+      <c r="S146" s="35" t="inlineStr">
+        <is>
+          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="29" customHeight="1">
+      <c r="A147" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use and distance, diesel cars</t>
+        </is>
+      </c>
+      <c r="B147" s="35" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="C147" s="35" t="inlineStr">
+        <is>
+          <t>litres per 100 km; km</t>
+        </is>
+      </c>
+      <c r="D147" s="35" t="inlineStr">
+        <is>
+          <t>2010 fleet</t>
+        </is>
+      </c>
+      <c r="E147" s="44" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K147" s="35" t="n"/>
+      <c r="L147" s="35" t="n"/>
+      <c r="M147" s="35" t="n"/>
+      <c r="N147" s="35" t="n"/>
+      <c r="O147" s="35" t="n"/>
+      <c r="P147" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q147" s="35" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018), vehicle parc model</t>
+        </is>
+      </c>
+      <c r="R147" s="35" t="inlineStr"/>
+      <c r="S147" s="35" t="inlineStr">
+        <is>
+          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="29" customHeight="1">
+      <c r="A148" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use and distance, diesel cars</t>
+        </is>
+      </c>
+      <c r="B148" s="35" t="inlineStr">
+        <is>
+          <t>km a year</t>
+        </is>
+      </c>
+      <c r="C148" s="35" t="inlineStr">
+        <is>
+          <t>litres per 100 km; km</t>
+        </is>
+      </c>
+      <c r="D148" s="35" t="inlineStr">
+        <is>
+          <t>2010 fleet</t>
+        </is>
+      </c>
+      <c r="E148" s="36" t="n">
+        <v>16748</v>
+      </c>
+      <c r="K148" s="35" t="n"/>
+      <c r="L148" s="35" t="n"/>
+      <c r="M148" s="35" t="n"/>
+      <c r="N148" s="35" t="n"/>
+      <c r="O148" s="35" t="n"/>
+      <c r="P148" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q148" s="35" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018), vehicle parc model</t>
+        </is>
+      </c>
+      <c r="R148" s="35" t="inlineStr"/>
+      <c r="S148" s="35" t="inlineStr">
+        <is>
+          <t>One year only. All 24 vehicle types are in the file and on the Vehicle history sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="29" customHeight="1">
+      <c r="A149" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use of new light vehicles: average change</t>
+        </is>
+      </c>
+      <c r="B149" s="35" t="inlineStr">
+        <is>
+          <t>New light-duty vehicles</t>
+        </is>
+      </c>
+      <c r="C149" s="35" t="inlineStr">
+        <is>
+          <t>% a year</t>
+        </is>
+      </c>
+      <c r="D149" s="35" t="inlineStr">
+        <is>
+          <t>2005-2019</t>
+        </is>
+      </c>
+      <c r="E149" s="44" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="K149" s="35" t="n"/>
+      <c r="L149" s="35" t="n"/>
+      <c r="M149" s="35" t="n"/>
+      <c r="N149" s="35" t="n"/>
+      <c r="O149" s="35" t="n"/>
+      <c r="P149" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q149" s="35" t="inlineStr">
+        <is>
+          <t>IEA, Fuel economy in South Africa (Global Fuel Economy Initiative 2021)</t>
+        </is>
+      </c>
+      <c r="R149" s="35" t="inlineStr"/>
+      <c r="S149" s="35" t="inlineStr">
+        <is>
+          <t>The model assumes 0.5 to 1.5% a year, so the observed rate sits inside the model's range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="29" customHeight="1">
+      <c r="A150" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use of new passenger cars</t>
+        </is>
+      </c>
+      <c r="B150" s="35" t="inlineStr">
+        <is>
+          <t>New passenger cars</t>
+        </is>
+      </c>
+      <c r="C150" s="35" t="inlineStr">
+        <is>
+          <t>litres per 100 km</t>
+        </is>
+      </c>
+      <c r="D150" s="35" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E150" s="44" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K150" s="35" t="n"/>
+      <c r="L150" s="35" t="n"/>
+      <c r="M150" s="35" t="n"/>
+      <c r="N150" s="35" t="n"/>
+      <c r="O150" s="35" t="n"/>
+      <c r="P150" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q150" s="35" t="inlineStr">
+        <is>
+          <t>ICCT white paper, South Africa's new passenger vehicle CO2 emission standards (January 2018)</t>
+        </is>
+      </c>
+      <c r="R150" s="35" t="inlineStr">
+        <is>
+          <t>PDF p.5</t>
+        </is>
+      </c>
+      <c r="S150" s="35" t="inlineStr">
+        <is>
+          <t>148 g CO2 per km on the older European test cycle, which reads lower than the worldwide cycle. From naamsa data.</t>
         </is>
       </c>
     </row>
     <row r="151" ht="29" customHeight="1">
       <c r="A151" s="35" t="inlineStr">
         <is>
-          <t>Mining, manufacturing and agriculture: activity and diesel per unit</t>
+          <t>Fuel use of trucks, lightest to heaviest class</t>
         </is>
       </c>
       <c r="B151" s="35" t="inlineStr">
         <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="C151" s="35" t="inlineStr"/>
+          <t>Diesel trucks, class 1 of nine</t>
+        </is>
+      </c>
+      <c r="C151" s="35" t="inlineStr">
+        <is>
+          <t>litres per 100 km, fleet average</t>
+        </is>
+      </c>
       <c r="D151" s="35" t="inlineStr">
         <is>
-          <t>2012-2025</t>
-        </is>
-      </c>
-      <c r="E151" s="35" t="inlineStr">
-        <is>
-          <t>On the Sector history sheet</t>
-        </is>
+          <t>2010 fleet</t>
+        </is>
+      </c>
+      <c r="E151" s="44" t="n">
+        <v>17.3</v>
       </c>
       <c r="K151" s="35" t="n"/>
       <c r="L151" s="35" t="n"/>
@@ -24546,66 +24783,1437 @@
       </c>
       <c r="Q151" s="35" t="inlineStr">
         <is>
-          <t>Statistics South Africa (P2041, P3041.2, P0441); department energy balances</t>
+          <t>Stone et al. (2018), vehicle parc model</t>
         </is>
       </c>
       <c r="R151" s="35" t="inlineStr"/>
       <c r="S151" s="35" t="inlineStr">
         <is>
+          <t>One year only. Light commercial diesel vehicles use 12.4 and buses 32.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="29" customHeight="1">
+      <c r="A152" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use of trucks, lightest to heaviest class</t>
+        </is>
+      </c>
+      <c r="B152" s="35" t="inlineStr">
+        <is>
+          <t>Class 3</t>
+        </is>
+      </c>
+      <c r="C152" s="35" t="inlineStr">
+        <is>
+          <t>litres per 100 km, fleet average</t>
+        </is>
+      </c>
+      <c r="D152" s="35" t="inlineStr">
+        <is>
+          <t>2010 fleet</t>
+        </is>
+      </c>
+      <c r="E152" s="44" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="K152" s="35" t="n"/>
+      <c r="L152" s="35" t="n"/>
+      <c r="M152" s="35" t="n"/>
+      <c r="N152" s="35" t="n"/>
+      <c r="O152" s="35" t="n"/>
+      <c r="P152" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q152" s="35" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018), vehicle parc model</t>
+        </is>
+      </c>
+      <c r="R152" s="35" t="inlineStr"/>
+      <c r="S152" s="35" t="inlineStr">
+        <is>
+          <t>One year only. Light commercial diesel vehicles use 12.4 and buses 32.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="29" customHeight="1">
+      <c r="A153" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use of trucks, lightest to heaviest class</t>
+        </is>
+      </c>
+      <c r="B153" s="35" t="inlineStr">
+        <is>
+          <t>Class 6</t>
+        </is>
+      </c>
+      <c r="C153" s="35" t="inlineStr">
+        <is>
+          <t>litres per 100 km, fleet average</t>
+        </is>
+      </c>
+      <c r="D153" s="35" t="inlineStr">
+        <is>
+          <t>2010 fleet</t>
+        </is>
+      </c>
+      <c r="E153" s="44" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K153" s="35" t="n"/>
+      <c r="L153" s="35" t="n"/>
+      <c r="M153" s="35" t="n"/>
+      <c r="N153" s="35" t="n"/>
+      <c r="O153" s="35" t="n"/>
+      <c r="P153" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q153" s="35" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018), vehicle parc model</t>
+        </is>
+      </c>
+      <c r="R153" s="35" t="inlineStr"/>
+      <c r="S153" s="35" t="inlineStr">
+        <is>
+          <t>One year only. Light commercial diesel vehicles use 12.4 and buses 32.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="29" customHeight="1">
+      <c r="A154" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use of trucks, lightest to heaviest class</t>
+        </is>
+      </c>
+      <c r="B154" s="35" t="inlineStr">
+        <is>
+          <t>Class 9</t>
+        </is>
+      </c>
+      <c r="C154" s="35" t="inlineStr">
+        <is>
+          <t>litres per 100 km, fleet average</t>
+        </is>
+      </c>
+      <c r="D154" s="35" t="inlineStr">
+        <is>
+          <t>2010 fleet</t>
+        </is>
+      </c>
+      <c r="E154" s="44" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="K154" s="35" t="n"/>
+      <c r="L154" s="35" t="n"/>
+      <c r="M154" s="35" t="n"/>
+      <c r="N154" s="35" t="n"/>
+      <c r="O154" s="35" t="n"/>
+      <c r="P154" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q154" s="35" t="inlineStr">
+        <is>
+          <t>Stone et al. (2018), vehicle parc model</t>
+        </is>
+      </c>
+      <c r="R154" s="35" t="inlineStr"/>
+      <c r="S154" s="35" t="inlineStr">
+        <is>
+          <t>One year only. Light commercial diesel vehicles use 12.4 and buses 32.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="29" customHeight="1">
+      <c r="A155" s="35" t="inlineStr">
+        <is>
+          <t>Fuel use of new light vehicles: figure in use</t>
+        </is>
+      </c>
+      <c r="B155" s="35" t="inlineStr">
+        <is>
+          <t>New cars and light commercial vehicles</t>
+        </is>
+      </c>
+      <c r="C155" s="35" t="inlineStr">
+        <is>
+          <t>litres of petrol equivalent per 100 km</t>
+        </is>
+      </c>
+      <c r="D155" s="35" t="inlineStr">
+        <is>
+          <t>2019, used for later years</t>
+        </is>
+      </c>
+      <c r="E155" s="44" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K155" s="35" t="n"/>
+      <c r="L155" s="35" t="n"/>
+      <c r="M155" s="35" t="n"/>
+      <c r="N155" s="35" t="n"/>
+      <c r="O155" s="35" t="n"/>
+      <c r="P155" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q155" s="35" t="inlineStr">
+        <is>
+          <t>IEA, Fuel economy in South Africa (Global Fuel Economy Initiative 2021)</t>
+        </is>
+      </c>
+      <c r="R155" s="35" t="inlineStr"/>
+      <c r="S155" s="35" t="inlineStr">
+        <is>
+          <t>The latest published figure. Used as it stands for the years after 2019 (Manish, 8 October).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="29" customHeight="1">
+      <c r="A156" s="41" t="inlineStr">
+        <is>
+          <t>Fuel use of trucks, by year</t>
+        </is>
+      </c>
+      <c r="B156" s="41" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C156" s="41" t="inlineStr">
+        <is>
+          <t>litres per 100 km</t>
+        </is>
+      </c>
+      <c r="D156" s="41" t="inlineStr"/>
+      <c r="E156" s="41" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="K156" s="41" t="n"/>
+      <c r="L156" s="41" t="n"/>
+      <c r="M156" s="41" t="n"/>
+      <c r="N156" s="41" t="n"/>
+      <c r="O156" s="41" t="n"/>
+      <c r="P156" s="41" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q156" s="41" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="R156" s="41" t="inlineStr"/>
+      <c r="S156" s="41" t="inlineStr">
+        <is>
+          <t>Only the 2010 fleet figures above exist. No truck series by year was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="29" customHeight="1">
+      <c r="A157" s="35" t="inlineStr">
+        <is>
+          <t>Efficiency gain assumed in the model</t>
+        </is>
+      </c>
+      <c r="B157" s="35" t="inlineStr">
+        <is>
+          <t>New diesel vehicles, high demand case</t>
+        </is>
+      </c>
+      <c r="C157" s="35" t="inlineStr">
+        <is>
+          <t>% a year</t>
+        </is>
+      </c>
+      <c r="D157" s="35" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E157" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K157" s="35" t="n"/>
+      <c r="L157" s="35" t="n"/>
+      <c r="M157" s="35" t="n"/>
+      <c r="N157" s="35" t="n"/>
+      <c r="O157" s="35" t="n"/>
+      <c r="P157" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q157" s="35" t="inlineStr">
+        <is>
+          <t>Reatile workbook (model input)</t>
+        </is>
+      </c>
+      <c r="R157" s="35" t="inlineStr"/>
+      <c r="S157" s="35" t="inlineStr">
+        <is>
+          <t>A model setting with no source behind it. Nothing was found to confirm or replace it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="29" customHeight="1">
+      <c r="A158" s="35" t="inlineStr">
+        <is>
+          <t>Efficiency gain assumed in the model</t>
+        </is>
+      </c>
+      <c r="B158" s="35" t="inlineStr">
+        <is>
+          <t>New diesel vehicles, low demand case</t>
+        </is>
+      </c>
+      <c r="C158" s="35" t="inlineStr">
+        <is>
+          <t>% a year</t>
+        </is>
+      </c>
+      <c r="D158" s="35" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E158" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" s="35" t="n"/>
+      <c r="L158" s="35" t="n"/>
+      <c r="M158" s="35" t="n"/>
+      <c r="N158" s="35" t="n"/>
+      <c r="O158" s="35" t="n"/>
+      <c r="P158" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q158" s="35" t="inlineStr">
+        <is>
+          <t>Reatile workbook (model input)</t>
+        </is>
+      </c>
+      <c r="R158" s="35" t="inlineStr"/>
+      <c r="S158" s="35" t="inlineStr">
+        <is>
+          <t>A model setting with no source behind it. Nothing was found to confirm or replace it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="29" customHeight="1">
+      <c r="A159" s="35" t="inlineStr">
+        <is>
+          <t>Efficiency gain assumed in the model</t>
+        </is>
+      </c>
+      <c r="B159" s="35" t="inlineStr">
+        <is>
+          <t>New petrol vehicles, high demand case</t>
+        </is>
+      </c>
+      <c r="C159" s="35" t="inlineStr">
+        <is>
+          <t>% a year</t>
+        </is>
+      </c>
+      <c r="D159" s="35" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E159" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" s="35" t="n"/>
+      <c r="L159" s="35" t="n"/>
+      <c r="M159" s="35" t="n"/>
+      <c r="N159" s="35" t="n"/>
+      <c r="O159" s="35" t="n"/>
+      <c r="P159" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q159" s="35" t="inlineStr">
+        <is>
+          <t>Reatile workbook (model input)</t>
+        </is>
+      </c>
+      <c r="R159" s="35" t="inlineStr"/>
+      <c r="S159" s="35" t="inlineStr">
+        <is>
+          <t>A model setting with no source behind it. Nothing was found to confirm or replace it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="29" customHeight="1">
+      <c r="A160" s="35" t="inlineStr">
+        <is>
+          <t>Efficiency gain assumed in the model</t>
+        </is>
+      </c>
+      <c r="B160" s="35" t="inlineStr">
+        <is>
+          <t>New petrol vehicles, low demand case</t>
+        </is>
+      </c>
+      <c r="C160" s="35" t="inlineStr">
+        <is>
+          <t>% a year</t>
+        </is>
+      </c>
+      <c r="D160" s="35" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E160" s="44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K160" s="35" t="n"/>
+      <c r="L160" s="35" t="n"/>
+      <c r="M160" s="35" t="n"/>
+      <c r="N160" s="35" t="n"/>
+      <c r="O160" s="35" t="n"/>
+      <c r="P160" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q160" s="35" t="inlineStr">
+        <is>
+          <t>Reatile workbook (model input)</t>
+        </is>
+      </c>
+      <c r="R160" s="35" t="inlineStr"/>
+      <c r="S160" s="35" t="inlineStr">
+        <is>
+          <t>A model setting with no source behind it. Nothing was found to confirm or replace it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="33" t="inlineStr">
+        <is>
+          <t>Freight and rail</t>
+        </is>
+      </c>
+      <c r="B162" s="33" t="n"/>
+      <c r="C162" s="33" t="n"/>
+      <c r="D162" s="33" t="n"/>
+      <c r="E162" s="33" t="n"/>
+      <c r="F162" s="33" t="n"/>
+      <c r="G162" s="33" t="n"/>
+      <c r="H162" s="33" t="n"/>
+      <c r="I162" s="33" t="n"/>
+      <c r="J162" s="33" t="n"/>
+      <c r="K162" s="33" t="n"/>
+      <c r="L162" s="33" t="n"/>
+      <c r="M162" s="33" t="n"/>
+      <c r="N162" s="33" t="n"/>
+      <c r="O162" s="33" t="n"/>
+      <c r="P162" s="33" t="n"/>
+      <c r="Q162" s="33" t="n"/>
+      <c r="R162" s="33" t="n"/>
+      <c r="S162" s="33" t="n"/>
+      <c r="T162" s="33" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="34" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B163" s="34" t="inlineStr">
+        <is>
+          <t>Covers</t>
+        </is>
+      </c>
+      <c r="C163" s="34" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D163" s="34" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E163" s="42" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F163" s="42" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G163" s="42" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H163" s="42" t="n">
+        <v>2021</v>
+      </c>
+      <c r="I163" s="42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J163" s="42" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K163" s="42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L163" s="42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M163" s="34" t="n"/>
+      <c r="N163" s="34" t="n"/>
+      <c r="O163" s="34" t="n"/>
+      <c r="P163" s="34" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Q163" s="34" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="R163" s="34" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="S163" s="34" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="29" customHeight="1">
+      <c r="A164" s="35" t="inlineStr">
+        <is>
+          <t>Freight carried by road</t>
+        </is>
+      </c>
+      <c r="B164" s="35" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C164" s="35" t="inlineStr">
+        <is>
+          <t>million tonnes</t>
+        </is>
+      </c>
+      <c r="D164" s="35" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E164" s="35" t="n"/>
+      <c r="F164" s="35" t="n"/>
+      <c r="G164" s="35" t="n"/>
+      <c r="H164" s="35" t="n"/>
+      <c r="I164" s="35" t="n"/>
+      <c r="J164" s="35" t="n"/>
+      <c r="K164" s="61" t="n">
+        <v>980</v>
+      </c>
+      <c r="L164" s="61" t="n">
+        <v>976</v>
+      </c>
+      <c r="M164" s="35" t="n"/>
+      <c r="N164" s="35" t="n"/>
+      <c r="O164" s="35" t="n"/>
+      <c r="P164" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q164" s="35" t="inlineStr">
+        <is>
+          <t>Statistics South Africa, Land transport survey (P7162), December 2025</t>
+        </is>
+      </c>
+      <c r="R164" s="35" t="inlineStr">
+        <is>
+          <t>PDF p.7</t>
+        </is>
+      </c>
+      <c r="S164" s="35" t="inlineStr">
+        <is>
+          <t>Tonnes, not tonne-kilometres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="29" customHeight="1">
+      <c r="A165" s="35" t="inlineStr">
+        <is>
+          <t>Freight carried by rail</t>
+        </is>
+      </c>
+      <c r="B165" s="35" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C165" s="35" t="inlineStr">
+        <is>
+          <t>million tonnes</t>
+        </is>
+      </c>
+      <c r="D165" s="35" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E165" s="35" t="n"/>
+      <c r="F165" s="35" t="n"/>
+      <c r="G165" s="35" t="n"/>
+      <c r="H165" s="35" t="n"/>
+      <c r="I165" s="35" t="n"/>
+      <c r="J165" s="35" t="n"/>
+      <c r="K165" s="61" t="n">
+        <v>161</v>
+      </c>
+      <c r="L165" s="61" t="n">
+        <v>168</v>
+      </c>
+      <c r="M165" s="35" t="n"/>
+      <c r="N165" s="35" t="n"/>
+      <c r="O165" s="35" t="n"/>
+      <c r="P165" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q165" s="35" t="inlineStr">
+        <is>
+          <t>Statistics South Africa, Land transport survey (P7162), December 2025</t>
+        </is>
+      </c>
+      <c r="R165" s="35" t="inlineStr">
+        <is>
+          <t>PDF p.7</t>
+        </is>
+      </c>
+      <c r="S165" s="35" t="inlineStr">
+        <is>
+          <t>Tonnes, not tonne-kilometres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="15.5" customHeight="1">
+      <c r="A166" s="37" t="inlineStr">
+        <is>
+          <t>Rail's share of road and rail tonnes</t>
+        </is>
+      </c>
+      <c r="B166" s="37" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C166" s="37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D166" s="37" t="inlineStr">
+        <is>
+          <t>calendar years</t>
+        </is>
+      </c>
+      <c r="E166" s="37" t="n"/>
+      <c r="F166" s="37" t="n"/>
+      <c r="G166" s="37" t="n"/>
+      <c r="H166" s="37" t="n"/>
+      <c r="I166" s="37" t="n"/>
+      <c r="J166" s="37" t="n"/>
+      <c r="K166" s="40" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="L166" s="40" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M166" s="37" t="n"/>
+      <c r="N166" s="37" t="n"/>
+      <c r="O166" s="37" t="n"/>
+      <c r="P166" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q166" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the survey</t>
+        </is>
+      </c>
+      <c r="R166" s="37" t="inlineStr"/>
+      <c r="S166" s="37" t="inlineStr"/>
+    </row>
+    <row r="167" ht="29" customHeight="1">
+      <c r="A167" s="35" t="inlineStr">
+        <is>
+          <t>Freight carried by Transnet Freight Rail</t>
+        </is>
+      </c>
+      <c r="B167" s="35" t="inlineStr">
+        <is>
+          <t>Transnet Freight Rail, all freight</t>
+        </is>
+      </c>
+      <c r="C167" s="35" t="inlineStr">
+        <is>
+          <t>million tonnes</t>
+        </is>
+      </c>
+      <c r="D167" s="35" t="inlineStr">
+        <is>
+          <t>years to March</t>
+        </is>
+      </c>
+      <c r="E167" s="60" t="n">
+        <v>226.3</v>
+      </c>
+      <c r="F167" s="60" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="G167" s="60" t="n">
+        <v>212.4</v>
+      </c>
+      <c r="H167" s="60" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="I167" s="60" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="J167" s="60" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="K167" s="60" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="L167" s="60" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="M167" s="35" t="n"/>
+      <c r="N167" s="35" t="n"/>
+      <c r="O167" s="35" t="n"/>
+      <c r="P167" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q167" s="35" t="inlineStr">
+        <is>
+          <t>Transnet annual results 2025, presentation</t>
+        </is>
+      </c>
+      <c r="R167" s="35" t="inlineStr">
+        <is>
+          <t>PDF p.14</t>
+        </is>
+      </c>
+      <c r="S167" s="35" t="inlineStr">
+        <is>
+          <t>Fell by a third from 2018 to 2023 and has risen since. Export iron ore, export coal and general freight together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="15.5" customHeight="1">
+      <c r="A168" s="35" t="inlineStr">
+        <is>
+          <t>Fuel used by Transnet, all divisions</t>
+        </is>
+      </c>
+      <c r="B168" s="35" t="inlineStr">
+        <is>
+          <t>Transnet, all divisions</t>
+        </is>
+      </c>
+      <c r="C168" s="35" t="inlineStr">
+        <is>
+          <t>million litres</t>
+        </is>
+      </c>
+      <c r="D168" s="35" t="inlineStr">
+        <is>
+          <t>years to March</t>
+        </is>
+      </c>
+      <c r="E168" s="35" t="n"/>
+      <c r="F168" s="35" t="n"/>
+      <c r="G168" s="35" t="n"/>
+      <c r="H168" s="35" t="n"/>
+      <c r="I168" s="35" t="n"/>
+      <c r="J168" s="35" t="n"/>
+      <c r="K168" s="61" t="n">
+        <v>190</v>
+      </c>
+      <c r="L168" s="61" t="n">
+        <v>199</v>
+      </c>
+      <c r="M168" s="35" t="n"/>
+      <c r="N168" s="35" t="n"/>
+      <c r="O168" s="35" t="n"/>
+      <c r="P168" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q168" s="35" t="inlineStr">
+        <is>
+          <t>Transnet Integrated Report 2025</t>
+        </is>
+      </c>
+      <c r="R168" s="35" t="inlineStr">
+        <is>
+          <t>PDF p.73</t>
+        </is>
+      </c>
+      <c r="S168" s="35" t="inlineStr">
+        <is>
+          <t>Up 4.37%, mainly an 8.49% rise in fuel for traction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="34" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B169" s="34" t="inlineStr">
+        <is>
+          <t>Covers</t>
+        </is>
+      </c>
+      <c r="C169" s="34" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D169" s="34" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="E169" s="34" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="K169" s="34" t="n"/>
+      <c r="L169" s="34" t="n"/>
+      <c r="M169" s="34" t="n"/>
+      <c r="N169" s="34" t="n"/>
+      <c r="O169" s="34" t="n"/>
+      <c r="P169" s="34" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Q169" s="34" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="R169" s="34" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="S169" s="34" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="29" customHeight="1">
+      <c r="A170" s="35" t="inlineStr">
+        <is>
+          <t>Transnet's rail target</t>
+        </is>
+      </c>
+      <c r="B170" s="35" t="inlineStr">
+        <is>
+          <t>Transnet</t>
+        </is>
+      </c>
+      <c r="C170" s="35" t="inlineStr">
+        <is>
+          <t>million tonnes</t>
+        </is>
+      </c>
+      <c r="D170" s="35" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E170" s="36" t="n">
+        <v>250</v>
+      </c>
+      <c r="K170" s="35" t="n"/>
+      <c r="L170" s="35" t="n"/>
+      <c r="M170" s="35" t="n"/>
+      <c r="N170" s="35" t="n"/>
+      <c r="O170" s="35" t="n"/>
+      <c r="P170" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q170" s="35" t="inlineStr">
+        <is>
+          <t>Transnet annual results 2025, presentation</t>
+        </is>
+      </c>
+      <c r="R170" s="35" t="inlineStr">
+        <is>
+          <t>PDF p.36</t>
+        </is>
+      </c>
+      <c r="S170" s="35" t="inlineStr">
+        <is>
+          <t>Transnet 'aims to grow its capacity to handle 250 million tons'. The slide gives no year; Nigel cited 2030.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="29" customHeight="1">
+      <c r="A171" s="37" t="inlineStr">
+        <is>
+          <t>Extra rail freight if the target is met</t>
+        </is>
+      </c>
+      <c r="B171" s="37" t="inlineStr">
+        <is>
+          <t>Transnet Freight Rail</t>
+        </is>
+      </c>
+      <c r="C171" s="37" t="inlineStr">
+        <is>
+          <t>million tonnes</t>
+        </is>
+      </c>
+      <c r="D171" s="37" t="inlineStr">
+        <is>
+          <t>target less the year to March 2025</t>
+        </is>
+      </c>
+      <c r="E171" s="62" t="n">
+        <v>90</v>
+      </c>
+      <c r="K171" s="37" t="n"/>
+      <c r="L171" s="37" t="n"/>
+      <c r="M171" s="37" t="n"/>
+      <c r="N171" s="37" t="n"/>
+      <c r="O171" s="37" t="n"/>
+      <c r="P171" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q171" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the two rows above</t>
+        </is>
+      </c>
+      <c r="R171" s="37" t="inlineStr"/>
+      <c r="S171" s="37" t="inlineStr">
+        <is>
+          <t>About 9% of road freight tonnes. Not all of it would come from road.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="29" customHeight="1">
+      <c r="A172" s="35" t="inlineStr">
+        <is>
+          <t>Freight in tonne-kilometres</t>
+        </is>
+      </c>
+      <c r="B172" s="35" t="inlineStr">
+        <is>
+          <t>All freight</t>
+        </is>
+      </c>
+      <c r="C172" s="35" t="inlineStr">
+        <is>
+          <t>billion tonne-km</t>
+        </is>
+      </c>
+      <c r="D172" s="35" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="E172" s="36" t="n">
+        <v>446</v>
+      </c>
+      <c r="K172" s="35" t="n"/>
+      <c r="L172" s="35" t="n"/>
+      <c r="M172" s="35" t="n"/>
+      <c r="N172" s="35" t="n"/>
+      <c r="O172" s="35" t="n"/>
+      <c r="P172" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q172" s="35" t="inlineStr">
+        <is>
+          <t>Havenga et al., A proposed freight and passenger road-to-rail strategy for South Africa (SA-TIED)</t>
+        </is>
+      </c>
+      <c r="R172" s="35" t="inlineStr">
+        <is>
+          <t>PDF pp.17, 25</t>
+        </is>
+      </c>
+      <c r="S172" s="35" t="inlineStr">
+        <is>
+          <t>Line haul 305, last mile 132, pipelines and conveyors 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="29" customHeight="1">
+      <c r="A173" s="35" t="inlineStr">
+        <is>
+          <t>Freight in tonne-kilometres</t>
+        </is>
+      </c>
+      <c r="B173" s="35" t="inlineStr">
+        <is>
+          <t>rail-friendly freight</t>
+        </is>
+      </c>
+      <c r="C173" s="35" t="inlineStr">
+        <is>
+          <t>billion tonne-km</t>
+        </is>
+      </c>
+      <c r="D173" s="35" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="E173" s="36" t="n">
+        <v>181</v>
+      </c>
+      <c r="K173" s="35" t="n"/>
+      <c r="L173" s="35" t="n"/>
+      <c r="M173" s="35" t="n"/>
+      <c r="N173" s="35" t="n"/>
+      <c r="O173" s="35" t="n"/>
+      <c r="P173" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q173" s="35" t="inlineStr">
+        <is>
+          <t>Havenga et al., A proposed freight and passenger road-to-rail strategy for South Africa (SA-TIED)</t>
+        </is>
+      </c>
+      <c r="R173" s="35" t="inlineStr">
+        <is>
+          <t>PDF pp.17, 25</t>
+        </is>
+      </c>
+      <c r="S173" s="35" t="inlineStr">
+        <is>
+          <t>Line haul 305, last mile 132, pipelines and conveyors 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="29" customHeight="1">
+      <c r="A174" s="35" t="inlineStr">
+        <is>
+          <t>Freight in tonne-kilometres</t>
+        </is>
+      </c>
+      <c r="B174" s="35" t="inlineStr">
+        <is>
+          <t>carried by rail</t>
+        </is>
+      </c>
+      <c r="C174" s="35" t="inlineStr">
+        <is>
+          <t>billion tonne-km</t>
+        </is>
+      </c>
+      <c r="D174" s="35" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="E174" s="36" t="n">
+        <v>141</v>
+      </c>
+      <c r="K174" s="35" t="n"/>
+      <c r="L174" s="35" t="n"/>
+      <c r="M174" s="35" t="n"/>
+      <c r="N174" s="35" t="n"/>
+      <c r="O174" s="35" t="n"/>
+      <c r="P174" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q174" s="35" t="inlineStr">
+        <is>
+          <t>Havenga et al., A proposed freight and passenger road-to-rail strategy for South Africa (SA-TIED)</t>
+        </is>
+      </c>
+      <c r="R174" s="35" t="inlineStr">
+        <is>
+          <t>PDF pp.17, 25</t>
+        </is>
+      </c>
+      <c r="S174" s="35" t="inlineStr">
+        <is>
+          <t>Line haul 305, last mile 132, pipelines and conveyors 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="29" customHeight="1">
+      <c r="A175" s="35" t="inlineStr">
+        <is>
+          <t>General freight that rail should carry but does not</t>
+        </is>
+      </c>
+      <c r="B175" s="35" t="inlineStr">
+        <is>
+          <t>Rail-friendly general freight on road</t>
+        </is>
+      </c>
+      <c r="C175" s="35" t="inlineStr">
+        <is>
+          <t>billion tonne-km</t>
+        </is>
+      </c>
+      <c r="D175" s="35" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="E175" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="K175" s="35" t="n"/>
+      <c r="L175" s="35" t="n"/>
+      <c r="M175" s="35" t="n"/>
+      <c r="N175" s="35" t="n"/>
+      <c r="O175" s="35" t="n"/>
+      <c r="P175" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q175" s="35" t="inlineStr">
+        <is>
+          <t>Havenga et al., A proposed freight and passenger road-to-rail strategy for South Africa (SA-TIED)</t>
+        </is>
+      </c>
+      <c r="R175" s="35" t="inlineStr">
+        <is>
+          <t>PDF p.26</t>
+        </is>
+      </c>
+      <c r="S175" s="35" t="inlineStr">
+        <is>
+          <t>As the source states it: rail should have carried 47 and carried 18. This is the freight that a road-to-rail shift would move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="29" customHeight="1">
+      <c r="A176" s="41" t="inlineStr">
+        <is>
+          <t>Road freight in tonne-kilometres, by year</t>
+        </is>
+      </c>
+      <c r="B176" s="41" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C176" s="41" t="inlineStr">
+        <is>
+          <t>billion tonne-km</t>
+        </is>
+      </c>
+      <c r="D176" s="41" t="inlineStr"/>
+      <c r="E176" s="41" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="K176" s="41" t="n"/>
+      <c r="L176" s="41" t="n"/>
+      <c r="M176" s="41" t="n"/>
+      <c r="N176" s="41" t="n"/>
+      <c r="O176" s="41" t="n"/>
+      <c r="P176" s="41" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="Q176" s="41" t="inlineStr">
+        <is>
+          <t>None published as numbers</t>
+        </is>
+      </c>
+      <c r="R176" s="41" t="inlineStr"/>
+      <c r="S176" s="41" t="inlineStr">
+        <is>
+          <t>The research group that models it (GAIN, Stellenbosch) shows yearly charts but publishes figures for single years only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="42.5" customHeight="1">
+      <c r="A177" s="37" t="inlineStr">
+        <is>
+          <t>Diesel used by rail locomotives</t>
+        </is>
+      </c>
+      <c r="B177" s="37" t="inlineStr">
+        <is>
+          <t>Transnet Freight Rail</t>
+        </is>
+      </c>
+      <c r="C177" s="37" t="inlineStr">
+        <is>
+          <t>million litres</t>
+        </is>
+      </c>
+      <c r="D177" s="37" t="inlineStr">
+        <is>
+          <t>year to March 2025</t>
+        </is>
+      </c>
+      <c r="E177" s="62" t="n">
+        <v>138</v>
+      </c>
+      <c r="K177" s="37" t="n"/>
+      <c r="L177" s="37" t="n"/>
+      <c r="M177" s="37" t="n"/>
+      <c r="N177" s="37" t="n"/>
+      <c r="O177" s="37" t="n"/>
+      <c r="P177" s="37" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="Q177" s="37" t="inlineStr">
+        <is>
+          <t>199 million litres x 69.2% used for diesel traction (both from the Transnet report)</t>
+        </is>
+      </c>
+      <c r="R177" s="37" t="inlineStr">
+        <is>
+          <t>PDF p.73</t>
+        </is>
+      </c>
+      <c r="S177" s="37" t="inlineStr">
+        <is>
+          <t>About 1% of diesel sales. So freight moving to rail saves nearly all the road diesel it displaces. The rest is generators 13.8%, vehicle fleets 10.2%, marine diesel 6.7%, jet fuel 0.1%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="33" t="inlineStr">
+        <is>
+          <t>Sector activity</t>
+        </is>
+      </c>
+      <c r="B179" s="33" t="n"/>
+      <c r="C179" s="33" t="n"/>
+      <c r="D179" s="33" t="n"/>
+      <c r="E179" s="33" t="n"/>
+      <c r="F179" s="33" t="n"/>
+      <c r="G179" s="33" t="n"/>
+      <c r="H179" s="33" t="n"/>
+      <c r="I179" s="33" t="n"/>
+      <c r="J179" s="33" t="n"/>
+      <c r="K179" s="33" t="n"/>
+      <c r="L179" s="33" t="n"/>
+      <c r="M179" s="33" t="n"/>
+      <c r="N179" s="33" t="n"/>
+      <c r="O179" s="33" t="n"/>
+      <c r="P179" s="33" t="n"/>
+      <c r="Q179" s="33" t="n"/>
+      <c r="R179" s="33" t="n"/>
+      <c r="S179" s="33" t="n"/>
+      <c r="T179" s="33" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="34" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B180" s="34" t="inlineStr">
+        <is>
+          <t>Covers</t>
+        </is>
+      </c>
+      <c r="C180" s="34" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D180" s="34" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="E180" s="34" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="K180" s="34" t="n"/>
+      <c r="L180" s="34" t="n"/>
+      <c r="M180" s="34" t="n"/>
+      <c r="N180" s="34" t="n"/>
+      <c r="O180" s="34" t="n"/>
+      <c r="P180" s="34" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Q180" s="34" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="R180" s="34" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="S180" s="34" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="29" customHeight="1">
+      <c r="A181" s="35" t="inlineStr">
+        <is>
+          <t>Mining, manufacturing and agriculture: activity and diesel per unit</t>
+        </is>
+      </c>
+      <c r="B181" s="35" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C181" s="35" t="inlineStr"/>
+      <c r="D181" s="35" t="inlineStr">
+        <is>
+          <t>2012-2025</t>
+        </is>
+      </c>
+      <c r="E181" s="35" t="inlineStr">
+        <is>
+          <t>On the Sector history sheet</t>
+        </is>
+      </c>
+      <c r="K181" s="35" t="n"/>
+      <c r="L181" s="35" t="n"/>
+      <c r="M181" s="35" t="n"/>
+      <c r="N181" s="35" t="n"/>
+      <c r="O181" s="35" t="n"/>
+      <c r="P181" s="35" t="inlineStr">
+        <is>
+          <t>From source</t>
+        </is>
+      </c>
+      <c r="Q181" s="35" t="inlineStr">
+        <is>
+          <t>Statistics South Africa (P2041, P3041.2, P0441); department energy balances</t>
+        </is>
+      </c>
+      <c r="R181" s="35" t="inlineStr"/>
+      <c r="S181" s="35" t="inlineStr">
+        <is>
           <t>Diesel by sector is observed to 2021 only, the last energy balance.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="141">
     <mergeCell ref="E19:J19"/>
     <mergeCell ref="E143:J143"/>
     <mergeCell ref="E28:J28"/>
+    <mergeCell ref="E177:J177"/>
     <mergeCell ref="E60:J60"/>
     <mergeCell ref="E69:J69"/>
+    <mergeCell ref="E149:J149"/>
     <mergeCell ref="E30:J30"/>
     <mergeCell ref="E59:J59"/>
     <mergeCell ref="E77:J77"/>
+    <mergeCell ref="E133:J133"/>
     <mergeCell ref="E46:J46"/>
+    <mergeCell ref="E169:J169"/>
     <mergeCell ref="E61:J61"/>
     <mergeCell ref="E32:J32"/>
-    <mergeCell ref="E125:J125"/>
+    <mergeCell ref="E159:J159"/>
     <mergeCell ref="E97:J97"/>
     <mergeCell ref="E112:J112"/>
+    <mergeCell ref="E109:J109"/>
     <mergeCell ref="E47:J47"/>
     <mergeCell ref="E96:J96"/>
     <mergeCell ref="E145:J145"/>
-    <mergeCell ref="E139:J139"/>
     <mergeCell ref="E71:J71"/>
     <mergeCell ref="E129:J129"/>
+    <mergeCell ref="E111:J111"/>
+    <mergeCell ref="E24:J24"/>
     <mergeCell ref="E142:J142"/>
-    <mergeCell ref="E24:J24"/>
     <mergeCell ref="E98:J98"/>
+    <mergeCell ref="E181:J181"/>
     <mergeCell ref="E79:J79"/>
+    <mergeCell ref="E131:J131"/>
     <mergeCell ref="E88:J88"/>
     <mergeCell ref="E51:J51"/>
     <mergeCell ref="E82:J82"/>
-    <mergeCell ref="E140:J140"/>
+    <mergeCell ref="E171:J171"/>
+    <mergeCell ref="E153:J153"/>
+    <mergeCell ref="E180:J180"/>
     <mergeCell ref="E63:J63"/>
+    <mergeCell ref="E155:J155"/>
+    <mergeCell ref="E137:J137"/>
+    <mergeCell ref="E173:J173"/>
     <mergeCell ref="E65:J65"/>
     <mergeCell ref="E34:J34"/>
     <mergeCell ref="E105:J105"/>
     <mergeCell ref="E99:J99"/>
+    <mergeCell ref="E157:J157"/>
     <mergeCell ref="E49:J49"/>
     <mergeCell ref="E36:J36"/>
     <mergeCell ref="E45:J45"/>
     <mergeCell ref="E101:J101"/>
-    <mergeCell ref="E116:J116"/>
     <mergeCell ref="E113:J113"/>
     <mergeCell ref="E91:J91"/>
     <mergeCell ref="E100:J100"/>
+    <mergeCell ref="E136:J136"/>
     <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E115:J115"/>
     <mergeCell ref="E93:J93"/>
     <mergeCell ref="E37:J37"/>
     <mergeCell ref="E102:J102"/>
     <mergeCell ref="E21:J21"/>
-    <mergeCell ref="E122:J122"/>
     <mergeCell ref="E62:J62"/>
     <mergeCell ref="E14:J14"/>
     <mergeCell ref="E127:J127"/>
@@ -24615,58 +26223,67 @@
     <mergeCell ref="E38:J38"/>
     <mergeCell ref="E147:J147"/>
     <mergeCell ref="E87:J87"/>
+    <mergeCell ref="E156:J156"/>
+    <mergeCell ref="E170:J170"/>
     <mergeCell ref="E128:J128"/>
     <mergeCell ref="E40:J40"/>
     <mergeCell ref="E90:J90"/>
+    <mergeCell ref="E148:J148"/>
     <mergeCell ref="E104:J104"/>
     <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E119:J119"/>
+    <mergeCell ref="E110:J110"/>
+    <mergeCell ref="E154:J154"/>
     <mergeCell ref="E76:J76"/>
     <mergeCell ref="E25:J25"/>
     <mergeCell ref="E85:J85"/>
+    <mergeCell ref="E174:J174"/>
     <mergeCell ref="E66:J66"/>
     <mergeCell ref="E75:J75"/>
     <mergeCell ref="E18:J18"/>
     <mergeCell ref="E53:J53"/>
     <mergeCell ref="E146:J146"/>
     <mergeCell ref="E50:J50"/>
-    <mergeCell ref="E121:J121"/>
     <mergeCell ref="E130:J130"/>
     <mergeCell ref="E68:J68"/>
     <mergeCell ref="E151:J151"/>
-    <mergeCell ref="E117:J117"/>
     <mergeCell ref="E55:J55"/>
+    <mergeCell ref="E160:J160"/>
+    <mergeCell ref="E175:J175"/>
     <mergeCell ref="E52:J52"/>
     <mergeCell ref="E67:J67"/>
-    <mergeCell ref="E123:J123"/>
     <mergeCell ref="E92:J92"/>
     <mergeCell ref="E150:J150"/>
     <mergeCell ref="E39:J39"/>
+    <mergeCell ref="E132:J132"/>
     <mergeCell ref="E107:J107"/>
     <mergeCell ref="E20:J20"/>
     <mergeCell ref="E29:J29"/>
+    <mergeCell ref="E94:J94"/>
     <mergeCell ref="E103:J103"/>
+    <mergeCell ref="E152:J152"/>
     <mergeCell ref="E13:J13"/>
     <mergeCell ref="E84:J84"/>
     <mergeCell ref="E78:J78"/>
-    <mergeCell ref="E118:J118"/>
     <mergeCell ref="E31:J31"/>
-    <mergeCell ref="E114:J114"/>
+    <mergeCell ref="E176:J176"/>
+    <mergeCell ref="E158:J158"/>
     <mergeCell ref="E15:J15"/>
+    <mergeCell ref="E108:J108"/>
     <mergeCell ref="E86:J86"/>
     <mergeCell ref="E80:J80"/>
+    <mergeCell ref="E95:J95"/>
     <mergeCell ref="E89:J89"/>
     <mergeCell ref="E70:J70"/>
     <mergeCell ref="E144:J144"/>
     <mergeCell ref="E26:J26"/>
     <mergeCell ref="E57:J57"/>
-    <mergeCell ref="E124:J124"/>
     <mergeCell ref="E54:J54"/>
-    <mergeCell ref="E120:J120"/>
     <mergeCell ref="E72:J72"/>
     <mergeCell ref="E41:J41"/>
     <mergeCell ref="E16:J16"/>
     <mergeCell ref="E81:J81"/>
+    <mergeCell ref="E134:J134"/>
+    <mergeCell ref="E172:J172"/>
     <mergeCell ref="E56:J56"/>
     <mergeCell ref="E43:J43"/>
     <mergeCell ref="E58:J58"/>
@@ -24676,7 +26293,7 @@
     <mergeCell ref="E17:J17"/>
     <mergeCell ref="E126:J126"/>
     <mergeCell ref="E83:J83"/>
-    <mergeCell ref="E141:J141"/>
+    <mergeCell ref="E135:J135"/>
     <mergeCell ref="E35:J35"/>
     <mergeCell ref="E44:J44"/>
   </mergeCells>
@@ -24777,28 +26394,28 @@
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="B5" s="63" t="n">
+      <c r="B5" s="64" t="n">
         <v>3485272</v>
       </c>
-      <c r="C5" s="63" t="n">
+      <c r="C5" s="64" t="n">
         <v>936521</v>
       </c>
-      <c r="D5" s="63" t="n">
+      <c r="D5" s="64" t="n">
         <v>150862</v>
       </c>
-      <c r="E5" s="63" t="n">
+      <c r="E5" s="64" t="n">
         <v>20937</v>
       </c>
-      <c r="F5" s="63" t="n">
+      <c r="F5" s="64" t="n">
         <v>127451</v>
       </c>
-      <c r="G5" s="63" t="n">
+      <c r="G5" s="64" t="n">
         <v>158810</v>
       </c>
-      <c r="H5" s="63" t="n">
+      <c r="H5" s="64" t="n">
         <v>4919011</v>
       </c>
-      <c r="I5" s="64">
+      <c r="I5" s="65">
         <f>H5/H$14</f>
         <v/>
       </c>
@@ -24814,28 +26431,28 @@
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="B6" s="63" t="n">
+      <c r="B6" s="64" t="n">
         <v>1171505</v>
       </c>
-      <c r="C6" s="63" t="n">
+      <c r="C6" s="64" t="n">
         <v>411049</v>
       </c>
-      <c r="D6" s="63" t="n">
+      <c r="D6" s="64" t="n">
         <v>59557</v>
       </c>
-      <c r="E6" s="63" t="n">
+      <c r="E6" s="64" t="n">
         <v>8253</v>
       </c>
-      <c r="F6" s="63" t="n">
+      <c r="F6" s="64" t="n">
         <v>61665</v>
       </c>
-      <c r="G6" s="63" t="n">
+      <c r="G6" s="64" t="n">
         <v>39411</v>
       </c>
-      <c r="H6" s="63" t="n">
+      <c r="H6" s="64" t="n">
         <v>1783517</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="65">
         <f>H6/H$14</f>
         <v/>
       </c>
@@ -24851,28 +26468,28 @@
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="B7" s="63" t="n">
+      <c r="B7" s="64" t="n">
         <v>1448715</v>
       </c>
-      <c r="C7" s="63" t="n">
+      <c r="C7" s="64" t="n">
         <v>371420</v>
       </c>
-      <c r="D7" s="63" t="n">
+      <c r="D7" s="64" t="n">
         <v>50960</v>
       </c>
-      <c r="E7" s="63" t="n">
+      <c r="E7" s="64" t="n">
         <v>7463</v>
       </c>
-      <c r="F7" s="63" t="n">
+      <c r="F7" s="64" t="n">
         <v>41603</v>
       </c>
-      <c r="G7" s="63" t="n">
+      <c r="G7" s="64" t="n">
         <v>96388</v>
       </c>
-      <c r="H7" s="63" t="n">
+      <c r="H7" s="64" t="n">
         <v>2060254</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="65">
         <f>H7/H$14</f>
         <v/>
       </c>
@@ -24888,28 +26505,28 @@
           <t>Eastern Cape</t>
         </is>
       </c>
-      <c r="B8" s="63" t="n">
+      <c r="B8" s="64" t="n">
         <v>506193</v>
       </c>
-      <c r="C8" s="63" t="n">
+      <c r="C8" s="64" t="n">
         <v>212296</v>
       </c>
-      <c r="D8" s="63" t="n">
+      <c r="D8" s="64" t="n">
         <v>23146</v>
       </c>
-      <c r="E8" s="63" t="n">
+      <c r="E8" s="64" t="n">
         <v>4894</v>
       </c>
-      <c r="F8" s="63" t="n">
+      <c r="F8" s="64" t="n">
         <v>27406</v>
       </c>
-      <c r="G8" s="63" t="n">
+      <c r="G8" s="64" t="n">
         <v>21876</v>
       </c>
-      <c r="H8" s="63" t="n">
+      <c r="H8" s="64" t="n">
         <v>813557</v>
       </c>
-      <c r="I8" s="64">
+      <c r="I8" s="65">
         <f>H8/H$14</f>
         <v/>
       </c>
@@ -24925,28 +26542,28 @@
           <t>Mpumalanga</t>
         </is>
       </c>
-      <c r="B9" s="63" t="n">
+      <c r="B9" s="64" t="n">
         <v>477358</v>
       </c>
-      <c r="C9" s="63" t="n">
+      <c r="C9" s="64" t="n">
         <v>231790</v>
       </c>
-      <c r="D9" s="63" t="n">
+      <c r="D9" s="64" t="n">
         <v>41125</v>
       </c>
-      <c r="E9" s="63" t="n">
+      <c r="E9" s="64" t="n">
         <v>7812</v>
       </c>
-      <c r="F9" s="63" t="n">
+      <c r="F9" s="64" t="n">
         <v>28469</v>
       </c>
-      <c r="G9" s="63" t="n">
+      <c r="G9" s="64" t="n">
         <v>17205</v>
       </c>
-      <c r="H9" s="63" t="n">
+      <c r="H9" s="64" t="n">
         <v>830714</v>
       </c>
-      <c r="I9" s="64">
+      <c r="I9" s="65">
         <f>H9/H$14</f>
         <v/>
       </c>
@@ -24962,28 +26579,28 @@
           <t>Limpopo</t>
         </is>
       </c>
-      <c r="B10" s="63" t="n">
+      <c r="B10" s="64" t="n">
         <v>419050</v>
       </c>
-      <c r="C10" s="63" t="n">
+      <c r="C10" s="64" t="n">
         <v>260224</v>
       </c>
-      <c r="D10" s="63" t="n">
+      <c r="D10" s="64" t="n">
         <v>28357</v>
       </c>
-      <c r="E10" s="63" t="n">
+      <c r="E10" s="64" t="n">
         <v>7774</v>
       </c>
-      <c r="F10" s="63" t="n">
+      <c r="F10" s="64" t="n">
         <v>28651</v>
       </c>
-      <c r="G10" s="63" t="n">
+      <c r="G10" s="64" t="n">
         <v>9060</v>
       </c>
-      <c r="H10" s="63" t="n">
+      <c r="H10" s="64" t="n">
         <v>771478</v>
       </c>
-      <c r="I10" s="64">
+      <c r="I10" s="65">
         <f>H10/H$14</f>
         <v/>
       </c>
@@ -24999,28 +26616,28 @@
           <t>North West</t>
         </is>
       </c>
-      <c r="B11" s="63" t="n">
+      <c r="B11" s="64" t="n">
         <v>365628</v>
       </c>
-      <c r="C11" s="63" t="n">
+      <c r="C11" s="64" t="n">
         <v>168694</v>
       </c>
-      <c r="D11" s="63" t="n">
+      <c r="D11" s="64" t="n">
         <v>18997</v>
       </c>
-      <c r="E11" s="63" t="n">
+      <c r="E11" s="64" t="n">
         <v>4326</v>
       </c>
-      <c r="F11" s="63" t="n">
+      <c r="F11" s="64" t="n">
         <v>22262</v>
       </c>
-      <c r="G11" s="63" t="n">
+      <c r="G11" s="64" t="n">
         <v>13126</v>
       </c>
-      <c r="H11" s="63" t="n">
+      <c r="H11" s="64" t="n">
         <v>614380</v>
       </c>
-      <c r="I11" s="64">
+      <c r="I11" s="65">
         <f>H11/H$14</f>
         <v/>
       </c>
@@ -25036,28 +26653,28 @@
           <t>Free State</t>
         </is>
       </c>
-      <c r="B12" s="63" t="n">
+      <c r="B12" s="64" t="n">
         <v>328418</v>
       </c>
-      <c r="C12" s="63" t="n">
+      <c r="C12" s="64" t="n">
         <v>138820</v>
       </c>
-      <c r="D12" s="63" t="n">
+      <c r="D12" s="64" t="n">
         <v>26190</v>
       </c>
-      <c r="E12" s="63" t="n">
+      <c r="E12" s="64" t="n">
         <v>3425</v>
       </c>
-      <c r="F12" s="63" t="n">
+      <c r="F12" s="64" t="n">
         <v>12679</v>
       </c>
-      <c r="G12" s="63" t="n">
+      <c r="G12" s="64" t="n">
         <v>16810</v>
       </c>
-      <c r="H12" s="63" t="n">
+      <c r="H12" s="64" t="n">
         <v>561774</v>
       </c>
-      <c r="I12" s="64">
+      <c r="I12" s="65">
         <f>H12/H$14</f>
         <v/>
       </c>
@@ -25073,28 +26690,28 @@
           <t>Northern Cape</t>
         </is>
       </c>
-      <c r="B13" s="63" t="n">
+      <c r="B13" s="64" t="n">
         <v>138453</v>
       </c>
-      <c r="C13" s="63" t="n">
+      <c r="C13" s="64" t="n">
         <v>85733</v>
       </c>
-      <c r="D13" s="63" t="n">
+      <c r="D13" s="64" t="n">
         <v>9855</v>
       </c>
-      <c r="E13" s="63" t="n">
+      <c r="E13" s="64" t="n">
         <v>1988</v>
       </c>
-      <c r="F13" s="63" t="n">
+      <c r="F13" s="64" t="n">
         <v>6811</v>
       </c>
-      <c r="G13" s="63" t="n">
+      <c r="G13" s="64" t="n">
         <v>7123</v>
       </c>
-      <c r="H13" s="63" t="n">
+      <c r="H13" s="64" t="n">
         <v>259795</v>
       </c>
-      <c r="I13" s="64">
+      <c r="I13" s="65">
         <f>H13/H$14</f>
         <v/>
       </c>
@@ -25110,35 +26727,35 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="B14" s="65">
+      <c r="B14" s="66">
         <f>SUM(B5:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="65">
+      <c r="C14" s="66">
         <f>SUM(C5:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="65">
+      <c r="D14" s="66">
         <f>SUM(D5:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="65">
+      <c r="E14" s="66">
         <f>SUM(E5:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="65">
+      <c r="F14" s="66">
         <f>SUM(F5:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="65">
+      <c r="G14" s="66">
         <f>SUM(G5:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="65">
+      <c r="H14" s="66">
         <f>SUM(H5:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="64">
+      <c r="I14" s="65">
         <f>H14/H$14</f>
         <v/>
       </c>
@@ -25202,17 +26819,17 @@
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="B18" s="63" t="n">
+      <c r="B18" s="64" t="n">
         <v>3466725</v>
       </c>
-      <c r="C18" s="63" t="n">
+      <c r="C18" s="64" t="n">
         <v>1142275</v>
       </c>
-      <c r="D18" s="65">
+      <c r="D18" s="66">
         <f>B18+C18</f>
         <v/>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="65">
         <f>C18/D18</f>
         <v/>
       </c>
@@ -25228,17 +26845,17 @@
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="B19" s="63" t="n">
+      <c r="B19" s="64" t="n">
         <v>1181017</v>
       </c>
-      <c r="C19" s="63" t="n">
+      <c r="C19" s="64" t="n">
         <v>459888</v>
       </c>
-      <c r="D19" s="65">
+      <c r="D19" s="66">
         <f>B19+C19</f>
         <v/>
       </c>
-      <c r="E19" s="64">
+      <c r="E19" s="65">
         <f>C19/D19</f>
         <v/>
       </c>
@@ -25254,17 +26871,17 @@
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="B20" s="63" t="n">
+      <c r="B20" s="64" t="n">
         <v>1426954</v>
       </c>
-      <c r="C20" s="63" t="n">
+      <c r="C20" s="64" t="n">
         <v>507006</v>
       </c>
-      <c r="D20" s="65">
+      <c r="D20" s="66">
         <f>B20+C20</f>
         <v/>
       </c>
-      <c r="E20" s="64">
+      <c r="E20" s="65">
         <f>C20/D20</f>
         <v/>
       </c>
@@ -25280,17 +26897,17 @@
           <t>Eastern Cape</t>
         </is>
       </c>
-      <c r="B21" s="63" t="n">
+      <c r="B21" s="64" t="n">
         <v>550085</v>
       </c>
-      <c r="C21" s="63" t="n">
+      <c r="C21" s="64" t="n">
         <v>233959</v>
       </c>
-      <c r="D21" s="65">
+      <c r="D21" s="66">
         <f>B21+C21</f>
         <v/>
       </c>
-      <c r="E21" s="64">
+      <c r="E21" s="65">
         <f>C21/D21</f>
         <v/>
       </c>
@@ -25306,17 +26923,17 @@
           <t>Mpumalanga</t>
         </is>
       </c>
-      <c r="B22" s="63" t="n">
+      <c r="B22" s="64" t="n">
         <v>529640</v>
       </c>
-      <c r="C22" s="63" t="n">
+      <c r="C22" s="64" t="n">
         <v>281750</v>
       </c>
-      <c r="D22" s="65">
+      <c r="D22" s="66">
         <f>B22+C22</f>
         <v/>
       </c>
-      <c r="E22" s="64">
+      <c r="E22" s="65">
         <f>C22/D22</f>
         <v/>
       </c>
@@ -25332,17 +26949,17 @@
           <t>Limpopo</t>
         </is>
       </c>
-      <c r="B23" s="63" t="n">
+      <c r="B23" s="64" t="n">
         <v>482248</v>
       </c>
-      <c r="C23" s="63" t="n">
+      <c r="C23" s="64" t="n">
         <v>240595</v>
       </c>
-      <c r="D23" s="65">
+      <c r="D23" s="66">
         <f>B23+C23</f>
         <v/>
       </c>
-      <c r="E23" s="64">
+      <c r="E23" s="65">
         <f>C23/D23</f>
         <v/>
       </c>
@@ -25358,17 +26975,17 @@
           <t>North West</t>
         </is>
       </c>
-      <c r="B24" s="63" t="n">
+      <c r="B24" s="64" t="n">
         <v>404398</v>
       </c>
-      <c r="C24" s="63" t="n">
+      <c r="C24" s="64" t="n">
         <v>184614</v>
       </c>
-      <c r="D24" s="65">
+      <c r="D24" s="66">
         <f>B24+C24</f>
         <v/>
       </c>
-      <c r="E24" s="64">
+      <c r="E24" s="65">
         <f>C24/D24</f>
         <v/>
       </c>
@@ -25384,17 +27001,17 @@
           <t>Free State</t>
         </is>
       </c>
-      <c r="B25" s="63" t="n">
+      <c r="B25" s="64" t="n">
         <v>358000</v>
       </c>
-      <c r="C25" s="63" t="n">
+      <c r="C25" s="64" t="n">
         <v>189266</v>
       </c>
-      <c r="D25" s="65">
+      <c r="D25" s="66">
         <f>B25+C25</f>
         <v/>
       </c>
-      <c r="E25" s="64">
+      <c r="E25" s="65">
         <f>C25/D25</f>
         <v/>
       </c>
@@ -25410,17 +27027,17 @@
           <t>Northern Cape</t>
         </is>
       </c>
-      <c r="B26" s="63" t="n">
+      <c r="B26" s="64" t="n">
         <v>156705</v>
       </c>
-      <c r="C26" s="63" t="n">
+      <c r="C26" s="64" t="n">
         <v>96193</v>
       </c>
-      <c r="D26" s="65">
+      <c r="D26" s="66">
         <f>B26+C26</f>
         <v/>
       </c>
-      <c r="E26" s="64">
+      <c r="E26" s="65">
         <f>C26/D26</f>
         <v/>
       </c>
@@ -25436,19 +27053,19 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="B27" s="65">
+      <c r="B27" s="66">
         <f>SUM(B18:B26)</f>
         <v/>
       </c>
-      <c r="C27" s="65">
+      <c r="C27" s="66">
         <f>SUM(C18:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="65">
+      <c r="D27" s="66">
         <f>B27+C27</f>
         <v/>
       </c>
-      <c r="E27" s="64">
+      <c r="E27" s="65">
         <f>C27/D27</f>
         <v/>
       </c>

--- a/output/delivered/Data_requests_DR01_DR04_DR07_DR08_2026_10_09.xlsx
+++ b/output/delivered/Data_requests_DR01_DR04_DR07_DR08_2026_10_09.xlsx
@@ -698,14 +698,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Data requests DR01, DR04, DR07 and DR08</t>
+          <t>Master data book: sourced data for the South Africa story</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Petrol and diesel only. Every figure names its source. Built by python -m lfm.scripts.build_data_requests_workbook --vintage 2026.</t>
+          <t>The one place to look for a sourced figure, set out by data request (DR01, DR04, DR07, DR08). Petrol and diesel only. Every figure names its source. Built by python -m lfm.scripts.build_data_requests_workbook --vintage 2026; do not edit by hand.</t>
         </is>
       </c>
     </row>
@@ -19070,7 +19070,7 @@
     <row r="62">
       <c r="A62" s="47" t="inlineStr">
         <is>
-          <t>69A</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="B62" s="36" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="D62" s="36" t="inlineStr">
         <is>
-          <t>Kenhardt (west of 20o longitude)</t>
+          <t>Gordonia (north of 27o30' latitude)</t>
         </is>
       </c>
       <c r="E62" s="59" t="n">
@@ -19105,7 +19105,7 @@
     <row r="63">
       <c r="A63" s="47" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>69A</t>
         </is>
       </c>
       <c r="B63" s="36" t="inlineStr">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="D63" s="36" t="inlineStr">
         <is>
-          <t>Gordonia (north of 27o30' latitude)</t>
+          <t>Kenhardt (west of 20o longitude)</t>
         </is>
       </c>
       <c r="E63" s="59" t="n">
